--- a/datos.xlsx
+++ b/datos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/T/BDESIGN/DASHBOARD/__INTERACTIVO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825B1C07-2403-9547-B3E6-FE502F4DE4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60557EDF-ED13-6241-955E-69A3D347C55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="17300" windowHeight="21680" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="113">
   <si>
     <t>PLANTILLA DASHBOARD BDESIGN</t>
   </si>
@@ -192,6 +192,15 @@
     <t>Tipología</t>
   </si>
   <si>
+    <t>Enero 2026</t>
+  </si>
+  <si>
+    <t>Febrero 2026</t>
+  </si>
+  <si>
+    <t>Marzo 2026</t>
+  </si>
+  <si>
     <t>Total YTD</t>
   </si>
   <si>
@@ -252,9 +261,6 @@
     <t>Métrica</t>
   </si>
   <si>
-    <t>Días medios de entrega</t>
-  </si>
-  <si>
     <t>MEDIA YTD</t>
   </si>
   <si>
@@ -351,19 +357,28 @@
     <t>Marbella</t>
   </si>
   <si>
+    <t>Abril 206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días medios de entrega </t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>Trabajos externalizados</t>
+  </si>
+  <si>
+    <t>Enero</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
     <t>Abril</t>
-  </si>
-  <si>
-    <t>Enero</t>
-  </si>
-  <si>
-    <t>Febrero</t>
-  </si>
-  <si>
-    <t>Marzo</t>
-  </si>
-  <si>
-    <t>Trabajos externalizados</t>
   </si>
   <si>
     <t>Freelance</t>
@@ -483,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -505,6 +520,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -800,12 +818,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -816,31 +834,31 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -851,71 +869,71 @@
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -926,51 +944,51 @@
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
     </row>
     <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -981,71 +999,71 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -1088,54 +1106,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>51</v>
+      </c>
+      <c r="E3" s="9">
+        <v>46113</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B4" s="8">
-        <v>23</v>
+        <f>23+7</f>
+        <v>30</v>
       </c>
       <c r="C4" s="8">
-        <v>28</v>
+        <f>28+10</f>
+        <v>38</v>
       </c>
       <c r="D4" s="8">
-        <v>23</v>
+        <f>23+8</f>
+        <v>31</v>
       </c>
       <c r="E4" s="8">
-        <v>26</v>
-      </c>
-      <c r="F4" s="9">
+        <f>26+9</f>
+        <v>35</v>
+      </c>
+      <c r="F4" s="10">
         <f t="shared" ref="F4:F18" si="0">SUM(B4:E4)</f>
-        <v>100</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1143,25 +1165,28 @@
         <v>45</v>
       </c>
       <c r="B5" s="8">
-        <v>25</v>
+        <f>25+1</f>
+        <v>26</v>
       </c>
       <c r="C5" s="8">
         <v>21</v>
       </c>
       <c r="D5" s="8">
-        <v>22</v>
+        <f>22+1</f>
+        <v>23</v>
       </c>
       <c r="E5" s="8">
-        <v>7</v>
-      </c>
-      <c r="F5" s="9">
-        <f t="shared" si="0"/>
-        <v>75</v>
+        <f>7+1</f>
+        <v>8</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" si="0"/>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" s="8">
         <v>11</v>
@@ -1173,100 +1198,115 @@
         <v>12</v>
       </c>
       <c r="E6" s="8">
-        <v>13</v>
-      </c>
-      <c r="F6" s="9">
-        <f t="shared" si="0"/>
-        <v>58</v>
+        <f>13+2</f>
+        <v>15</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7" s="8">
-        <v>13</v>
+        <f>13+2</f>
+        <v>15</v>
       </c>
       <c r="C7" s="8">
-        <v>8</v>
+        <f>8+7</f>
+        <v>15</v>
       </c>
       <c r="D7" s="8">
-        <v>11</v>
+        <f>11+7</f>
+        <v>18</v>
       </c>
       <c r="E7" s="8">
-        <v>11</v>
-      </c>
-      <c r="F7" s="9">
-        <f t="shared" si="0"/>
-        <v>43</v>
+        <f>11+10</f>
+        <v>21</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="0"/>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8" s="8">
+        <f>9+1</f>
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <f>6+1</f>
+        <v>7</v>
+      </c>
+      <c r="D8" s="8">
+        <f>7+2</f>
         <v>9</v>
-      </c>
-      <c r="C8" s="8">
-        <v>6</v>
-      </c>
-      <c r="D8" s="8">
-        <v>7</v>
       </c>
       <c r="E8" s="8">
         <v>11</v>
       </c>
-      <c r="F8" s="9">
-        <f t="shared" si="0"/>
-        <v>33</v>
+      <c r="F8" s="10">
+        <f t="shared" si="0"/>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B9" s="8">
-        <v>5</v>
+        <f>5+1</f>
+        <v>6</v>
       </c>
       <c r="C9" s="8">
-        <v>8</v>
+        <f>8+1</f>
+        <v>9</v>
       </c>
       <c r="D9" s="8">
         <v>6</v>
       </c>
       <c r="E9" s="8">
-        <v>6</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f>6+2</f>
+        <v>8</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B10" s="8">
-        <v>9</v>
+        <f>9+1</f>
+        <v>10</v>
       </c>
       <c r="C10" s="8">
-        <v>4</v>
+        <f>4+6</f>
+        <v>10</v>
       </c>
       <c r="D10" s="8">
-        <v>4</v>
+        <f>4+3</f>
+        <v>7</v>
       </c>
       <c r="E10" s="8">
-        <v>3</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>3+2</f>
+        <v>5</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
@@ -1280,33 +1320,35 @@
       <c r="E11" s="8">
         <v>6</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8">
-        <v>4</v>
+        <f>4+1</f>
+        <v>5</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
       <c r="E12" s="8">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
@@ -1318,14 +1360,14 @@
       <c r="E13" s="8">
         <v>3</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="8">
         <v>2</v>
@@ -1334,34 +1376,36 @@
         <v>2</v>
       </c>
       <c r="D14" s="8">
-        <v>2</v>
+        <f>2+2</f>
+        <v>4</v>
       </c>
       <c r="E14" s="8"/>
-      <c r="F14" s="9">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="F14" s="10">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="8">
-        <v>3</v>
+        <f>3+1</f>
+        <v>4</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8">
         <v>1</v>
       </c>
-      <c r="F15" s="9">
-        <f t="shared" si="0"/>
-        <v>4</v>
+      <c r="F15" s="10">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B16" s="8">
         <v>3</v>
@@ -1371,49 +1415,51 @@
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="9">
+      <c r="F16" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
       <c r="E17" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="F17" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="11">
+        <v>57</v>
+      </c>
+      <c r="B18" s="12">
         <f>SUM(B4:B17)</f>
-        <v>111</v>
-      </c>
-      <c r="C18" s="11">
+        <v>126</v>
+      </c>
+      <c r="C18" s="12">
         <f>SUM(C4:C17)</f>
-        <v>107</v>
-      </c>
-      <c r="D18" s="11">
+        <v>132</v>
+      </c>
+      <c r="D18" s="12">
         <f>SUM(D4:D17)</f>
-        <v>92</v>
-      </c>
-      <c r="E18" s="11">
+        <v>116</v>
+      </c>
+      <c r="E18" s="12">
         <f>SUM(E4:E17)</f>
-        <v>90</v>
-      </c>
-      <c r="F18" s="11">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>117</v>
+      </c>
+      <c r="F18" s="12">
+        <f t="shared" si="0"/>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -1422,6 +1468,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <ignoredErrors>
+    <ignoredError sqref="B9" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1435,59 +1484,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>51</v>
+      </c>
+      <c r="E3" s="9">
+        <v>46113</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="8">
+        <f>25+1</f>
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
+        <f>24+1</f>
         <v>25</v>
       </c>
-      <c r="C4" s="8">
-        <v>24</v>
-      </c>
       <c r="D4" s="8">
+        <f>20+1</f>
+        <v>21</v>
+      </c>
+      <c r="E4" s="8">
+        <f>18+2</f>
         <v>20</v>
-      </c>
-      <c r="E4" s="8">
-        <v>18</v>
       </c>
       <c r="F4" s="8">
         <f t="shared" ref="F4:F24" si="0">SUM(B4:E4)</f>
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8">
         <v>19</v>
@@ -1508,7 +1561,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B6" s="8">
         <v>14</v>
@@ -1529,7 +1582,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
@@ -1541,16 +1594,17 @@
         <v>16</v>
       </c>
       <c r="E7" s="8">
-        <v>13</v>
+        <f>13+1</f>
+        <v>14</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="8">
         <v>10</v>
@@ -1571,7 +1625,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B9" s="8">
         <v>12</v>
@@ -1592,28 +1646,30 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" s="8">
-        <v>5</v>
+        <f>5+1</f>
+        <v>6</v>
       </c>
       <c r="C10" s="8">
         <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>5</v>
+        <f>5+3</f>
+        <v>8</v>
       </c>
       <c r="E10" s="8">
         <v>3</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B11" s="8">
         <v>5</v>
@@ -1634,7 +1690,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
@@ -1655,51 +1711,62 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>3</v>
+        <f>3+12</f>
+        <v>15</v>
       </c>
       <c r="C13" s="8">
-        <v>2</v>
+        <f>2+23</f>
+        <v>25</v>
       </c>
       <c r="D13" s="8">
-        <v>3</v>
-      </c>
-      <c r="E13" s="8"/>
+        <f>3+18</f>
+        <v>21</v>
+      </c>
+      <c r="E13" s="8">
+        <f>0+23</f>
+        <v>23</v>
+      </c>
       <c r="F13" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8">
-        <v>1</v>
+        <f>1+2</f>
+        <v>3</v>
       </c>
       <c r="C14" s="8">
         <v>2</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="8">
+        <f>0+2</f>
+        <v>2</v>
+      </c>
       <c r="E14" s="8">
         <v>3</v>
       </c>
       <c r="F14" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" s="8">
         <v>2</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="D15" s="8">
         <v>1</v>
@@ -1709,12 +1776,12 @@
       </c>
       <c r="F15" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8">
@@ -1733,7 +1800,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B17" s="8">
         <v>3</v>
@@ -1750,7 +1817,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8">
@@ -1767,7 +1834,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
@@ -1784,7 +1851,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
@@ -1801,7 +1868,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B21" s="8">
         <v>1</v>
@@ -1820,7 +1887,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1835,7 +1902,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
@@ -1850,42 +1917,45 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8">
         <v>1</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="8">
+        <f>0+1</f>
+        <v>1</v>
+      </c>
       <c r="F24" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(B4:B24)</f>
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(C4:C24)</f>
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(D4:D24)</f>
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E25" s="4">
         <f>SUM(E4:E24)</f>
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="F25" s="4">
         <f>SUM(F4:F24)</f>
-        <v>400</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -1907,38 +1977,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="8">
         <v>160</v>
@@ -1959,7 +2029,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8">
         <v>62.8</v>
@@ -1980,28 +2050,32 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="8">
-        <v>58</v>
+        <f>58+0.5</f>
+        <v>58.5</v>
       </c>
       <c r="C6" s="8">
-        <v>102.5</v>
+        <f>102.5+3</f>
+        <v>105.5</v>
       </c>
       <c r="D6" s="8">
-        <v>26.5</v>
+        <f>26.5+1</f>
+        <v>27.5</v>
       </c>
       <c r="E6" s="8">
-        <v>62.25</v>
+        <f>62.25+9.25</f>
+        <v>71.5</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>249.25</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B7" s="8">
         <v>52</v>
@@ -2022,7 +2096,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B8" s="8">
         <v>79</v>
@@ -2034,16 +2108,17 @@
         <v>29.25</v>
       </c>
       <c r="E8" s="8">
-        <v>43.5</v>
+        <f>43.5+3</f>
+        <v>46.5</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>223.25</v>
+        <v>226.25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B9" s="8">
         <v>2</v>
@@ -2064,28 +2139,30 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" s="8">
-        <v>40.5</v>
+        <f>40.5+20.5</f>
+        <v>61</v>
       </c>
       <c r="C10" s="8">
         <v>38</v>
       </c>
       <c r="D10" s="8">
-        <v>16.75</v>
+        <f>16.75+32</f>
+        <v>48.75</v>
       </c>
       <c r="E10" s="8">
         <v>8</v>
       </c>
       <c r="F10" s="7">
         <f t="shared" si="0"/>
-        <v>103.25</v>
+        <v>155.75</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B11" s="8">
         <v>36</v>
@@ -2106,7 +2183,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B12" s="8">
         <v>21.5</v>
@@ -2127,7 +2204,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="8">
         <v>17.5</v>
@@ -2148,7 +2225,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2165,7 +2242,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8">
@@ -2180,7 +2257,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8">
@@ -2199,26 +2276,31 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B17" s="8">
-        <v>16.75</v>
-      </c>
-      <c r="C17" s="8"/>
+        <f>16.75+22</f>
+        <v>38.75</v>
+      </c>
+      <c r="C17" s="8">
+        <f>0+4</f>
+        <v>4</v>
+      </c>
       <c r="D17" s="8">
-        <v>3</v>
+        <f>3+4.25</f>
+        <v>7.25</v>
       </c>
       <c r="E17" s="8">
         <v>4</v>
       </c>
       <c r="F17" s="7">
         <f t="shared" si="0"/>
-        <v>23.75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B18" s="8">
         <v>4</v>
@@ -2237,41 +2319,48 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="B19" s="8">
+        <v>73</v>
+      </c>
       <c r="C19" s="8">
-        <v>5.75</v>
+        <f>5.75+241</f>
+        <v>246.75</v>
       </c>
       <c r="D19" s="8">
-        <v>13.5</v>
+        <f>13.5+208</f>
+        <v>221.5</v>
       </c>
       <c r="E19" s="8">
-        <v>3.75</v>
+        <f>3.75+126</f>
+        <v>129.75</v>
       </c>
       <c r="F19" s="7">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>671</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
         <v>13</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="8">
+        <v>6</v>
+      </c>
       <c r="F20" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2286,7 +2375,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8">
@@ -2303,13 +2392,14 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
       </c>
       <c r="C23" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="D23" s="8">
         <v>5</v>
@@ -2319,12 +2409,12 @@
       </c>
       <c r="F23" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B24" s="8">
         <v>3</v>
@@ -2341,7 +2431,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8">
@@ -2358,27 +2448,27 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B26" s="4">
         <f>SUM(B4:B25)</f>
-        <v>554.04999999999995</v>
+        <v>670.05</v>
       </c>
       <c r="C26" s="4">
         <f>SUM(C4:C25)</f>
-        <v>580.25</v>
+        <v>829.25</v>
       </c>
       <c r="D26" s="4">
         <f>SUM(D4:D25)</f>
-        <v>672.5</v>
+        <v>917.75</v>
       </c>
       <c r="E26" s="4">
         <f>SUM(E4:E25)</f>
-        <v>627.25</v>
+        <v>771.5</v>
       </c>
       <c r="F26" s="4">
         <f t="shared" si="0"/>
-        <v>2434.0500000000002</v>
+        <v>3188.55</v>
       </c>
     </row>
   </sheetData>
@@ -2400,86 +2490,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>51</v>
+      </c>
+      <c r="E3" s="9">
+        <v>46113</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B4" s="8">
-        <v>77</v>
+        <f>77+12</f>
+        <v>89</v>
       </c>
       <c r="C4" s="8">
-        <v>73</v>
+        <f>73+21</f>
+        <v>94</v>
       </c>
       <c r="D4" s="8">
-        <v>67</v>
+        <f>67+24</f>
+        <v>91</v>
       </c>
       <c r="E4" s="8">
-        <v>59</v>
+        <f>59+26</f>
+        <v>85</v>
       </c>
       <c r="F4" s="7">
         <f t="shared" ref="F4:F9" si="0">SUM(B4:E4)</f>
-        <v>276</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B5" s="8">
-        <v>27</v>
+        <f>27+3</f>
+        <v>30</v>
       </c>
       <c r="C5" s="8">
-        <v>14</v>
+        <f>14+3</f>
+        <v>17</v>
       </c>
       <c r="D5" s="8">
-        <v>18</v>
+        <f>18+2</f>
+        <v>20</v>
       </c>
       <c r="E5" s="8">
-        <v>15</v>
+        <f>15+2</f>
+        <v>17</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="8">
-        <v>4</v>
+        <f>4+3</f>
+        <v>7</v>
       </c>
       <c r="C6" s="8">
-        <v>13</v>
+        <f>13+1</f>
+        <v>14</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
@@ -2489,15 +2589,16 @@
       </c>
       <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8">
+        <f>5</f>
         <v>5</v>
       </c>
       <c r="D7" s="8">
@@ -2511,7 +2612,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="8">
         <v>3</v>
@@ -2528,27 +2629,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B9" s="4">
         <f>SUM(B4:B8)</f>
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4">
         <f>SUM(C4:C8)</f>
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D9" s="4">
         <f>SUM(D4:D8)</f>
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="E9" s="4">
         <f>SUM(E4:E8)</f>
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -2570,59 +2671,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="8">
-        <v>2.0299999999999998</v>
+        <v>105</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="8">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="D4" s="8">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="E4" s="8">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="17">
+        <v>72</v>
+      </c>
+      <c r="B5" s="18">
         <f>AVERAGE(B4:E4)</f>
-        <v>2.19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+        <v>2.1366666666666667</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2644,75 +2745,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>51</v>
+      </c>
+      <c r="E3" s="9">
+        <v>46113</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8">
-        <v>25</v>
+        <f>25+1</f>
+        <v>26</v>
       </c>
       <c r="C4" s="8">
         <v>21</v>
       </c>
       <c r="D4" s="8">
-        <v>22</v>
+        <f>22+1</f>
+        <v>23</v>
       </c>
       <c r="E4" s="8">
-        <v>7</v>
+        <f>7+1</f>
+        <v>8</v>
       </c>
       <c r="F4" s="7">
         <f>SUM(B4:E4)</f>
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8">
-        <v>13.75</v>
+        <f>13.75+12</f>
+        <v>25.75</v>
       </c>
       <c r="C5" s="8">
         <v>23.25</v>
       </c>
       <c r="D5" s="8">
-        <v>19</v>
+        <f>19+15.5</f>
+        <v>34.5</v>
       </c>
       <c r="E5" s="8">
-        <v>5</v>
+        <f>5+26</f>
+        <v>31</v>
       </c>
       <c r="F5" s="7">
         <f>SUM(B5:E5)</f>
-        <v>61</v>
+        <v>114.5</v>
       </c>
     </row>
   </sheetData>
@@ -2725,41 +2832,41 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B72C5E1-D8EF-BD4B-9990-2660E94F2C3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3724B3-610D-B645-9E33-D85F4FB536C4}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60557EDF-ED13-6241-955E-69A3D347C55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E25689-27D6-4745-B27E-49A030120589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="17300" windowHeight="21680" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="112">
   <si>
     <t>PLANTILLA DASHBOARD BDESIGN</t>
   </si>
@@ -355,9 +355,6 @@
   </si>
   <si>
     <t>Marbella</t>
-  </si>
-  <si>
-    <t>Abril 206</t>
   </si>
   <si>
     <t xml:space="preserve">Días medios de entrega </t>
@@ -533,14 +530,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -818,12 +815,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -834,31 +831,31 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
     </row>
     <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
     </row>
     <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -869,71 +866,71 @@
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -944,51 +941,51 @@
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
     </row>
     <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
     </row>
     <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -999,89 +996,74 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
@@ -1090,6 +1072,21 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1498,16 +1495,16 @@
         <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46113</v>
+        <v>109</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>52</v>
@@ -1991,16 +1988,16 @@
         <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>52</v>
@@ -2504,16 +2501,16 @@
         <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46113</v>
+        <v>109</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>52</v>
@@ -2684,24 +2681,24 @@
         <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>105</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>106</v>
       </c>
       <c r="C4" s="8">
         <v>2.25</v>
@@ -2759,16 +2756,16 @@
         <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46113</v>
+        <v>109</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>52</v>
@@ -2838,7 +2835,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2849,16 +2846,16 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>52</v>
@@ -2866,7 +2863,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E25689-27D6-4745-B27E-49A030120589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3C1EF-0AE6-8646-A550-4243EF3E28C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="17300" windowHeight="21680" tabRatio="500" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="17300" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="109">
   <si>
     <t>PLANTILLA DASHBOARD BDESIGN</t>
   </si>
@@ -190,15 +190,6 @@
   </si>
   <si>
     <t>Tipología</t>
-  </si>
-  <si>
-    <t>Enero 2026</t>
-  </si>
-  <si>
-    <t>Febrero 2026</t>
-  </si>
-  <si>
-    <t>Marzo 2026</t>
   </si>
   <si>
     <t>Total YTD</t>
@@ -530,14 +521,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -815,12 +806,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -831,31 +822,31 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -866,71 +857,71 @@
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -941,51 +932,51 @@
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
     </row>
     <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -996,74 +987,89 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
@@ -1072,21 +1078,6 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1117,24 +1108,24 @@
         <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46113</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8">
         <f>23+7</f>
@@ -1183,7 +1174,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B6" s="8">
         <v>11</v>
@@ -1205,7 +1196,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B7" s="8">
         <f>13+2</f>
@@ -1230,7 +1221,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B8" s="8">
         <f>9+1</f>
@@ -1254,7 +1245,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B9" s="8">
         <f>5+1</f>
@@ -1278,7 +1269,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B10" s="8">
         <f>9+1</f>
@@ -1303,7 +1294,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B11" s="8">
         <v>3</v>
@@ -1324,7 +1315,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B12" s="8">
         <f>4+1</f>
@@ -1345,7 +1336,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
@@ -1364,7 +1355,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B14" s="8">
         <v>2</v>
@@ -1384,7 +1375,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B15" s="8">
         <f>3+1</f>
@@ -1402,7 +1393,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B16" s="8">
         <v>3</v>
@@ -1419,7 +1410,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1436,7 +1427,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B18" s="12">
         <f>SUM(B4:B17)</f>
@@ -1482,7 +1473,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1492,27 +1483,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8">
         <f>25+1</f>
@@ -1537,7 +1528,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="8">
         <v>19</v>
@@ -1558,7 +1549,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6" s="8">
         <v>14</v>
@@ -1579,7 +1570,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
@@ -1601,7 +1592,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B8" s="8">
         <v>10</v>
@@ -1622,7 +1613,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B9" s="8">
         <v>12</v>
@@ -1643,7 +1634,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B10" s="8">
         <f>5+1</f>
@@ -1666,7 +1657,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B11" s="8">
         <v>5</v>
@@ -1687,7 +1678,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
@@ -1708,7 +1699,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8">
         <f>3+12</f>
@@ -1733,7 +1724,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B14" s="8">
         <f>1+2</f>
@@ -1756,7 +1747,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B15" s="8">
         <v>2</v>
@@ -1778,7 +1769,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8">
@@ -1797,7 +1788,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" s="8">
         <v>3</v>
@@ -1814,7 +1805,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8">
@@ -1831,7 +1822,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
@@ -1848,7 +1839,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
@@ -1865,7 +1856,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B21" s="8">
         <v>1</v>
@@ -1884,7 +1875,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1899,7 +1890,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
@@ -1914,7 +1905,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -1932,7 +1923,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(B4:B24)</f>
@@ -1975,7 +1966,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1985,27 +1976,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B4" s="8">
         <v>160</v>
@@ -2026,7 +2017,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="8">
         <v>62.8</v>
@@ -2047,7 +2038,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B6" s="8">
         <f>58+0.5</f>
@@ -2072,7 +2063,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8">
         <v>52</v>
@@ -2093,7 +2084,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B8" s="8">
         <v>79</v>
@@ -2115,7 +2106,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B9" s="8">
         <v>2</v>
@@ -2136,7 +2127,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B10" s="8">
         <f>40.5+20.5</f>
@@ -2159,7 +2150,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B11" s="8">
         <v>36</v>
@@ -2180,7 +2171,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8">
         <v>21.5</v>
@@ -2201,7 +2192,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B13" s="8">
         <v>17.5</v>
@@ -2222,7 +2213,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2239,7 +2230,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8">
@@ -2254,7 +2245,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8">
@@ -2273,7 +2264,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B17" s="8">
         <f>16.75+22</f>
@@ -2297,7 +2288,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B18" s="8">
         <v>4</v>
@@ -2316,7 +2307,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B19" s="8">
         <v>73</v>
@@ -2340,7 +2331,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
@@ -2357,7 +2348,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2372,7 +2363,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8">
@@ -2389,7 +2380,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8">
         <v>1</v>
@@ -2411,7 +2402,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" s="8">
         <v>3</v>
@@ -2428,7 +2419,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8">
@@ -2445,7 +2436,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B26" s="4">
         <f>SUM(B4:B25)</f>
@@ -2488,7 +2479,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2501,24 +2492,24 @@
         <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B4" s="8">
         <f>77+12</f>
@@ -2543,7 +2534,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5" s="8">
         <f>27+3</f>
@@ -2568,7 +2559,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B6" s="8">
         <f>4+3</f>
@@ -2591,7 +2582,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8">
@@ -2609,7 +2600,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B8" s="8">
         <v>3</v>
@@ -2626,7 +2617,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4">
         <f>SUM(B4:B8)</f>
@@ -2669,7 +2660,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2678,27 +2669,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C4" s="8">
         <v>2.25</v>
@@ -2712,7 +2703,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="18">
         <f>AVERAGE(B4:E4)</f>
@@ -2743,7 +2734,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2753,27 +2744,27 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B4" s="8">
         <f>25+1</f>
@@ -2797,7 +2788,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B5" s="8">
         <f>13.75+12</f>
@@ -2835,7 +2826,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2846,24 +2837,24 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/T/BDESIGN/DASHBOARD/__INTERACTIVO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3C1EF-0AE6-8646-A550-4243EF3E28C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D243B-7CED-E64E-BDFF-E29013313185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="17300" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
   <si>
     <t>PLANTILLA DASHBOARD BDESIGN</t>
   </si>
@@ -252,6 +252,9 @@
     <t>Métrica</t>
   </si>
   <si>
+    <t>Días medios de entrega</t>
+  </si>
+  <si>
     <t>MEDIA YTD</t>
   </si>
   <si>
@@ -348,28 +351,31 @@
     <t>Marbella</t>
   </si>
   <si>
-    <t xml:space="preserve">Días medios de entrega </t>
-  </si>
-  <si>
-    <t>1,97</t>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Enero</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>Marzo</t>
   </si>
   <si>
     <t>Trabajos externalizados</t>
   </si>
   <si>
-    <t>Enero</t>
-  </si>
-  <si>
-    <t>Febrero</t>
-  </si>
-  <si>
-    <t>Marzo</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
     <t>Freelance</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Sevilla</t>
   </si>
 </sst>
 </file>
@@ -486,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -508,9 +514,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -521,14 +524,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -806,12 +809,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -822,31 +825,31 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -857,71 +860,71 @@
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
     </row>
     <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -932,51 +935,51 @@
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
     </row>
     <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
     </row>
     <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
     </row>
     <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
     </row>
     <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
     </row>
     <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -987,89 +990,74 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
@@ -1078,6 +1066,21 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1086,93 +1089,96 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>107</v>
+      <c r="E3" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B4" s="8">
-        <f>23+7</f>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8">
-        <f>28+10</f>
+        <v>28</v>
+      </c>
+      <c r="D4" s="8">
+        <v>23</v>
+      </c>
+      <c r="E4" s="8">
+        <v>25</v>
+      </c>
+      <c r="F4" s="8">
         <v>38</v>
       </c>
-      <c r="D4" s="8">
-        <f>23+8</f>
-        <v>31</v>
-      </c>
-      <c r="E4" s="8">
-        <f>26+9</f>
-        <v>35</v>
-      </c>
-      <c r="F4" s="10">
-        <f t="shared" ref="F4:F18" si="0">SUM(B4:E4)</f>
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="9">
+        <f>SUM(B4:F4)</f>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="8">
-        <f>25+1</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="8">
         <v>21</v>
       </c>
       <c r="D5" s="8">
-        <f>22+1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="8">
-        <f>7+1</f>
-        <v>8</v>
-      </c>
-      <c r="F5" s="10">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="F5" s="8">
+        <v>20</v>
+      </c>
+      <c r="G5" s="9">
+        <f>SUM(B5:F5)</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1186,352 +1192,367 @@
         <v>12</v>
       </c>
       <c r="E6" s="8">
-        <f>13+2</f>
-        <v>15</v>
-      </c>
-      <c r="F6" s="10">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
+        <v>18</v>
+      </c>
+      <c r="G6" s="9">
+        <f>SUM(B6:F6)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="8">
-        <f>13+2</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8">
-        <f>8+7</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D7" s="8">
-        <f>11+7</f>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8">
-        <f>11+10</f>
-        <v>21</v>
-      </c>
-      <c r="F7" s="10">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="F7" s="8">
+        <v>12</v>
+      </c>
+      <c r="G7" s="9">
+        <f>SUM(B7:F7)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="8">
-        <f>9+1</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="8">
-        <f>6+1</f>
+        <v>6</v>
+      </c>
+      <c r="D8" s="8">
         <v>7</v>
-      </c>
-      <c r="D8" s="8">
-        <f>7+2</f>
-        <v>9</v>
       </c>
       <c r="E8" s="8">
         <v>11</v>
       </c>
-      <c r="F8" s="10">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8" s="8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="9">
+        <f>SUM(B8:F8)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="8">
-        <f>5+1</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="8">
-        <f>8+1</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="8">
         <v>6</v>
       </c>
       <c r="E9" s="8">
-        <f>6+2</f>
+        <v>6</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3</v>
+      </c>
+      <c r="G9" s="9">
+        <f>SUM(B9:F9)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="8">
+        <v>3</v>
+      </c>
+      <c r="C10" s="8">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8">
+        <v>4</v>
+      </c>
+      <c r="E10" s="8">
+        <v>6</v>
+      </c>
+      <c r="F10" s="8">
         <v>8</v>
       </c>
-      <c r="F9" s="10">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="8">
-        <f>9+1</f>
-        <v>10</v>
-      </c>
-      <c r="C10" s="8">
-        <f>4+6</f>
-        <v>10</v>
-      </c>
-      <c r="D10" s="8">
-        <f>4+3</f>
-        <v>7</v>
-      </c>
-      <c r="E10" s="8">
-        <f>3+2</f>
-        <v>5</v>
-      </c>
-      <c r="F10" s="10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="9">
+        <f>SUM(B10:F10)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>76</v>
       </c>
       <c r="B11" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C11" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="8">
         <v>4</v>
       </c>
       <c r="E11" s="8">
-        <v>6</v>
-      </c>
-      <c r="F11" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="F11" s="8">
+        <v>3</v>
+      </c>
+      <c r="G11" s="9">
+        <f>SUM(B11:F11)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8">
-        <f>4+1</f>
-        <v>5</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8">
-        <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="F12" s="10">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8">
+        <v>7</v>
+      </c>
+      <c r="G12" s="9">
+        <f>SUM(B12:F12)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="8">
-        <v>1</v>
-      </c>
-      <c r="C13" s="8">
-        <v>2</v>
-      </c>
-      <c r="D13" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
       <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9">
+        <f>SUM(B13:F13)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8">
         <v>3</v>
       </c>
-      <c r="F13" s="10">
-        <f t="shared" si="0"/>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="9">
+        <f>SUM(B14:F14)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="8">
+        <v>2</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9">
+        <f>SUM(B15:F15)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="8">
-        <v>2</v>
-      </c>
-      <c r="C14" s="8">
-        <v>2</v>
-      </c>
-      <c r="D14" s="8">
-        <f>2+2</f>
-        <v>4</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B15" s="8">
-        <f>3+1</f>
-        <v>4</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="10">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="B16" s="8">
         <v>3</v>
       </c>
-      <c r="C16" s="8">
-        <v>1</v>
-      </c>
+      <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
+        <f>SUM(B16:F16)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
+      <c r="D17" s="8"/>
       <c r="E17" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="8"/>
+      <c r="G17" s="10">
+        <f>SUM(B17:F17)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f>SUM(B4:B17)</f>
-        <v>126</v>
-      </c>
-      <c r="C18" s="12">
+        <v>112</v>
+      </c>
+      <c r="C18" s="11">
         <f>SUM(C4:C17)</f>
-        <v>132</v>
-      </c>
-      <c r="D18" s="12">
+        <v>107</v>
+      </c>
+      <c r="D18" s="11">
         <f>SUM(D4:D17)</f>
-        <v>116</v>
-      </c>
-      <c r="E18" s="12">
+        <v>92</v>
+      </c>
+      <c r="E18" s="11">
         <f>SUM(E4:E17)</f>
+        <v>89</v>
+      </c>
+      <c r="F18" s="11">
+        <f>SUM(F4:F17)</f>
         <v>117</v>
       </c>
-      <c r="F18" s="12">
-        <f t="shared" si="0"/>
-        <v>491</v>
+      <c r="G18" s="11">
+        <f>SUM(B18:F18)</f>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <ignoredErrors>
-    <ignoredError sqref="B9" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>107</v>
+      <c r="E3" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" s="8">
-        <f>25+1</f>
         <v>26</v>
       </c>
       <c r="C4" s="8">
-        <f>24+1</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="8">
-        <f>20+1</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="8">
-        <f>18+2</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4" s="8">
-        <f t="shared" ref="F4:F24" si="0">SUM(B4:E4)</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="G4" s="8">
+        <f>SUM(B4:F4)</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="8">
         <v>20</v>
@@ -1540,16 +1561,19 @@
         <v>7</v>
       </c>
       <c r="E5" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="G5" s="8">
+        <f>SUM(B5:F5)</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" s="8">
         <v>14</v>
@@ -1564,13 +1588,16 @@
         <v>9</v>
       </c>
       <c r="F6" s="8">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="G6" s="8">
+        <f>SUM(B6:F6)</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
@@ -1582,15 +1609,17 @@
         <v>16</v>
       </c>
       <c r="E7" s="8">
-        <f>13+1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
+        <f>SUM(B7:F7)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -1607,55 +1636,62 @@
         <v>10</v>
       </c>
       <c r="F8" s="8">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="G8" s="8">
+        <f>SUM(B8:F8)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B9" s="8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C9" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D9" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="G9" s="8">
+        <f>SUM(B9:F9)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>86</v>
       </c>
       <c r="B10" s="8">
-        <f>5+1</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C10" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" s="8">
-        <f>5+3</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
         <v>3</v>
       </c>
-      <c r="F10" s="8">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="8">
+        <f>SUM(B10:F10)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>87</v>
       </c>
@@ -1663,20 +1699,23 @@
         <v>5</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="8">
+        <v>5</v>
+      </c>
+      <c r="E11" s="8">
         <v>3</v>
       </c>
-      <c r="E11" s="8">
-        <v>5</v>
-      </c>
       <c r="F11" s="8">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="G11" s="8">
+        <f>SUM(B11:F11)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
@@ -1693,102 +1732,102 @@
         <v>4</v>
       </c>
       <c r="F12" s="8">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="G12" s="8">
+        <f>SUM(B12:F12)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <f>3+12</f>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C13" s="8">
-        <f>2+23</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D13" s="8">
-        <f>3+18</f>
-        <v>21</v>
-      </c>
-      <c r="E13" s="8">
-        <f>0+23</f>
-        <v>23</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E13" s="8"/>
       <c r="F13" s="8">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8">
+        <f>SUM(B13:F13)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="8">
-        <f>1+2</f>
+        <v>91</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8">
         <v>3</v>
       </c>
-      <c r="C14" s="8">
-        <v>2</v>
-      </c>
       <c r="D14" s="8">
-        <f>0+2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="F14" s="8">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="8">
+        <f>SUM(B14:F14)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8">
+        <v>3</v>
+      </c>
+      <c r="G15" s="8">
+        <f>SUM(B15:F15)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="8">
-        <v>2</v>
-      </c>
-      <c r="C15" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="8"/>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
       <c r="C16" s="8">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8">
         <v>3</v>
       </c>
-      <c r="D16" s="8">
-        <v>1</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
       <c r="F16" s="8">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="8">
+        <f>SUM(B16:F16)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="8">
         <v>3</v>
@@ -1799,30 +1838,38 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8">
-        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G17" s="8">
+        <f>SUM(B17:F17)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="8">
+        <v>2</v>
+      </c>
+      <c r="C18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8">
+        <f>SUM(B18:F18)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8">
-        <v>2</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8">
-        <v>2</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
@@ -1833,49 +1880,56 @@
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="8">
+        <f>SUM(B19:F19)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="8"/>
+        <v>96</v>
+      </c>
+      <c r="B20" s="8">
+        <v>1</v>
+      </c>
       <c r="C20" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="8">
         <v>1</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="8">
+        <f>SUM(B20:F20)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="8">
-        <v>1</v>
-      </c>
+      <c r="B21" s="8"/>
       <c r="C21" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="8">
         <v>1</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="8">
-        <f t="shared" si="0"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8">
+        <f>SUM(B21:F21)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1883,72 +1937,78 @@
         <v>2</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8">
+        <f>SUM(B22:F22)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="8">
-        <v>1</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="8">
+        <v>1</v>
+      </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="8">
+        <f>SUM(B23:F23)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="8"/>
+      <c r="B24" s="8">
+        <v>1</v>
+      </c>
       <c r="C24" s="8"/>
-      <c r="D24" s="8">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8">
-        <f>0+1</f>
-        <v>1</v>
-      </c>
-      <c r="F24" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8">
+        <f>SUM(B24:F24)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(B4:B24)</f>
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(C4:C24)</f>
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(D4:D24)</f>
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="E25" s="4">
         <f>SUM(E4:E24)</f>
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F25" s="4">
         <f>SUM(F4:F24)</f>
-        <v>492</v>
+        <v>116</v>
+      </c>
+      <c r="G25" s="4">
+        <f>SUM(B25:F25)</f>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1957,511 +2017,573 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" s="8">
+        <v>165.5</v>
+      </c>
+      <c r="C4" s="8">
+        <v>279.75</v>
+      </c>
+      <c r="D4" s="8">
+        <v>127</v>
+      </c>
+      <c r="E4" s="8">
         <v>160</v>
       </c>
-      <c r="C4" s="8">
-        <v>127</v>
-      </c>
-      <c r="D4" s="8">
-        <v>165.5</v>
-      </c>
-      <c r="E4" s="8">
-        <v>279.75</v>
-      </c>
-      <c r="F4" s="7">
-        <f t="shared" ref="F4:F26" si="0">SUM(B4:E4)</f>
-        <v>732.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F4" s="8">
+        <v>191</v>
+      </c>
+      <c r="G4" s="7">
+        <f>SUM(B4:F4)</f>
+        <v>923.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="8">
-        <v>62.8</v>
+        <v>149.75</v>
       </c>
       <c r="C5" s="8">
+        <v>25.5</v>
+      </c>
+      <c r="D5" s="8">
         <v>53.25</v>
       </c>
-      <c r="D5" s="8">
-        <v>147.75</v>
-      </c>
       <c r="E5" s="8">
-        <v>25.5</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="0"/>
-        <v>289.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60.8</v>
+      </c>
+      <c r="F5" s="8">
+        <v>110.25</v>
+      </c>
+      <c r="G5" s="7">
+        <f>SUM(B5:F5)</f>
+        <v>399.55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="8">
-        <f>58+0.5</f>
-        <v>58.5</v>
+        <v>26.5</v>
       </c>
       <c r="C6" s="8">
-        <f>102.5+3</f>
-        <v>105.5</v>
+        <v>62.25</v>
       </c>
       <c r="D6" s="8">
-        <f>26.5+1</f>
-        <v>27.5</v>
+        <v>102.5</v>
       </c>
       <c r="E6" s="8">
-        <f>62.25+9.25</f>
-        <v>71.5</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>263</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="F6" s="8">
+        <v>25.75</v>
+      </c>
+      <c r="G6" s="7">
+        <f>SUM(B6:F6)</f>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="8">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C7" s="8">
+        <v>65.5</v>
+      </c>
+      <c r="D7" s="8">
         <v>28</v>
       </c>
-      <c r="D7" s="8">
-        <v>89</v>
-      </c>
       <c r="E7" s="8">
-        <v>65.5</v>
-      </c>
-      <c r="F7" s="7">
-        <f t="shared" si="0"/>
-        <v>234.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="F7" s="8">
+        <v>19.75</v>
+      </c>
+      <c r="G7" s="7">
+        <f>SUM(B7:F7)</f>
+        <v>268.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" s="8">
-        <v>79</v>
+        <v>29.25</v>
       </c>
       <c r="C8" s="8">
+        <v>43.5</v>
+      </c>
+      <c r="D8" s="8">
         <v>71.5</v>
       </c>
-      <c r="D8" s="8">
-        <v>29.25</v>
-      </c>
       <c r="E8" s="8">
-        <f>43.5+3</f>
-        <v>46.5</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
+        <f>SUM(B8:F8)</f>
         <v>226.25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" s="8">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="C9" s="8">
+        <v>53.5</v>
+      </c>
+      <c r="D9" s="8">
         <v>28.5</v>
       </c>
-      <c r="D9" s="8">
-        <v>74</v>
-      </c>
       <c r="E9" s="8">
-        <v>53.5</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="0"/>
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8">
+        <v>24.75</v>
+      </c>
+      <c r="G9" s="7">
+        <f>SUM(B9:F9)</f>
+        <v>182.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="8">
-        <f>40.5+20.5</f>
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C10" s="8">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D10" s="8">
-        <f>16.75+32</f>
-        <v>48.75</v>
+        <v>34.5</v>
       </c>
       <c r="E10" s="8">
-        <v>8</v>
-      </c>
-      <c r="F10" s="7">
-        <f t="shared" si="0"/>
-        <v>155.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="F10" s="8">
+        <v>82</v>
+      </c>
+      <c r="G10" s="7">
+        <f>SUM(B10:F10)</f>
+        <v>171.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B11" s="8">
-        <v>36</v>
+        <v>16.75</v>
       </c>
       <c r="C11" s="8">
-        <v>34.5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="8">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E11" s="8">
-        <v>6</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" si="0"/>
-        <v>89.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>40.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>37.5</v>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(B11:F11)</f>
+        <v>140.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="8">
+        <v>24.25</v>
+      </c>
+      <c r="C12" s="8">
+        <v>15</v>
+      </c>
+      <c r="D12" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="E12" s="8">
         <v>21.5</v>
       </c>
-      <c r="C12" s="8">
-        <v>13.5</v>
-      </c>
-      <c r="D12" s="8">
-        <v>24.25</v>
-      </c>
-      <c r="E12" s="8">
-        <v>15</v>
-      </c>
-      <c r="F12" s="7">
-        <f t="shared" si="0"/>
-        <v>74.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="8">
+        <v>32.5</v>
+      </c>
+      <c r="G12" s="7">
+        <f>SUM(B12:F12)</f>
+        <v>106.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="8">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>13</v>
+      </c>
+      <c r="D13" s="8">
+        <v>18.25</v>
+      </c>
+      <c r="E13" s="8">
         <v>17.5</v>
       </c>
-      <c r="C13" s="8">
-        <v>18.25</v>
-      </c>
-      <c r="D13" s="8">
-        <v>9</v>
-      </c>
-      <c r="E13" s="8">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7">
-        <f t="shared" si="0"/>
-        <v>57.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="8">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7">
+        <f>SUM(B13:F13)</f>
+        <v>62.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8">
+      <c r="C14" s="8">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8">
+        <v>3</v>
+      </c>
+      <c r="F14" s="8">
+        <v>48</v>
+      </c>
+      <c r="G14" s="7">
+        <f>SUM(B14:F14)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="8">
         <v>39.5</v>
       </c>
-      <c r="E14" s="8">
+      <c r="C15" s="8">
         <v>8</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" si="0"/>
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8">
-        <v>24.25</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="7">
-        <f t="shared" si="0"/>
+      <c r="F15" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(B15:F15)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="C16" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="D16" s="8">
+        <v>8.75</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8">
+        <v>4</v>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(B16:F16)</f>
+        <v>27.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="C17" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="D17" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8">
+        <v>4</v>
+      </c>
+      <c r="G17" s="7">
+        <f>SUM(B17:F17)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="D18" s="8">
+        <v>5</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="G18" s="7">
+        <f>SUM(B18:F18)</f>
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="8">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8">
+        <v>16.75</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <f>SUM(B19:F19)</f>
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8">
         <v>24.25</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8">
-        <v>8.75</v>
-      </c>
-      <c r="D16" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="E16" s="8">
-        <v>10.5</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" si="0"/>
-        <v>23.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="8">
-        <f>16.75+22</f>
-        <v>38.75</v>
-      </c>
-      <c r="C17" s="8">
-        <f>0+4</f>
-        <v>4</v>
-      </c>
-      <c r="D17" s="8">
-        <f>3+4.25</f>
-        <v>7.25</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="8">
-        <v>4</v>
-      </c>
-      <c r="C18" s="8">
-        <v>5</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8">
-        <v>14.5</v>
-      </c>
-      <c r="F18" s="7">
-        <f t="shared" si="0"/>
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="8">
-        <v>73</v>
-      </c>
-      <c r="C19" s="8">
-        <f>5.75+241</f>
-        <v>246.75</v>
-      </c>
-      <c r="D19" s="8">
-        <f>13.5+208</f>
-        <v>221.5</v>
-      </c>
-      <c r="E19" s="8">
-        <f>3.75+126</f>
-        <v>129.75</v>
-      </c>
-      <c r="F19" s="7">
-        <f t="shared" si="0"/>
-        <v>671</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8">
-        <v>13</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8">
-        <v>6</v>
-      </c>
-      <c r="F20" s="7">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7">
+        <f>SUM(B20:F20)</f>
+        <v>24.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8">
+        <v>13</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
+        <f>SUM(B21:F21)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="8">
         <v>12</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7">
-        <f t="shared" si="0"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="7">
+        <f>SUM(B22:F22)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8">
+        <v>5</v>
+      </c>
+      <c r="D23" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="7">
+        <f>SUM(B23:F23)</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8">
-        <v>6.5</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8">
         <v>5</v>
       </c>
-      <c r="F22" s="7">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="8">
-        <v>1</v>
-      </c>
-      <c r="C23" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="G24" s="7">
+        <f>SUM(B24:F24)</f>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="8">
         <v>5</v>
       </c>
-      <c r="E23" s="8">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="8">
-        <v>3</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8">
-        <v>5</v>
-      </c>
-      <c r="F24" s="7">
-        <f t="shared" si="0"/>
+      <c r="C25" s="8">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="7">
+        <f>SUM(B25:F25)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8">
-        <v>1</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="F25" s="7">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7">
+        <f>SUM(B26:F26)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="4">
-        <f>SUM(B4:B25)</f>
-        <v>670.05</v>
-      </c>
-      <c r="C26" s="4">
-        <f>SUM(C4:C25)</f>
-        <v>829.25</v>
-      </c>
-      <c r="D26" s="4">
-        <f>SUM(D4:D25)</f>
-        <v>917.75</v>
-      </c>
-      <c r="E26" s="4">
-        <f>SUM(E4:E25)</f>
-        <v>771.5</v>
-      </c>
-      <c r="F26" s="4">
-        <f t="shared" si="0"/>
-        <v>3188.55</v>
+      <c r="B27" s="4">
+        <f>SUM(B4:B26)</f>
+        <v>674.5</v>
+      </c>
+      <c r="C27" s="4">
+        <f>SUM(C4:C26)</f>
+        <v>627.25</v>
+      </c>
+      <c r="D27" s="4">
+        <f>SUM(D4:D26)</f>
+        <v>580.25</v>
+      </c>
+      <c r="E27" s="4">
+        <f>SUM(E4:E26)</f>
+        <v>568.04999999999995</v>
+      </c>
+      <c r="F27" s="4">
+        <f>SUM(F4:F26)</f>
+        <v>603.25</v>
+      </c>
+      <c r="G27" s="4">
+        <f>SUM(B27:F27)</f>
+        <v>3053.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2470,104 +2592,104 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="8">
-        <f>77+12</f>
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C4" s="8">
-        <f>73+21</f>
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D4" s="8">
-        <f>67+24</f>
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E4" s="8">
-        <f>59+26</f>
-        <v>85</v>
-      </c>
-      <c r="F4" s="7">
-        <f t="shared" ref="F4:F9" si="0">SUM(B4:E4)</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="F4" s="8">
+        <v>90</v>
+      </c>
+      <c r="G4" s="7">
+        <f>SUM(B4:F4)</f>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B5" s="8">
-        <f>27+3</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="8">
-        <f>14+3</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" s="8">
-        <f>18+2</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" s="8">
-        <f>15+2</f>
-        <v>17</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F5" s="8">
+        <v>10</v>
+      </c>
+      <c r="G5" s="7">
+        <f>SUM(B5:F5)</f>
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B6" s="8">
-        <f>4+3</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="8">
-        <f>13+1</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
@@ -2575,32 +2697,37 @@
       <c r="E6" s="8">
         <v>16</v>
       </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6" s="8">
+        <v>13</v>
+      </c>
+      <c r="G6" s="7">
+        <f>SUM(B6:F6)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8">
-        <f>5</f>
         <v>5</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="7">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <f>SUM(B7:F7)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="8">
         <v>3</v>
@@ -2610,39 +2737,62 @@
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="F8" s="8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7">
+        <f>SUM(B8:F8)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <f>SUM(B9:F9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="4">
-        <f>SUM(B4:B8)</f>
-        <v>129</v>
-      </c>
-      <c r="C9" s="4">
-        <f>SUM(C4:C8)</f>
-        <v>132</v>
-      </c>
-      <c r="D9" s="4">
-        <f>SUM(D4:D8)</f>
-        <v>118</v>
-      </c>
-      <c r="E9" s="4">
-        <f>SUM(E4:E8)</f>
-        <v>118</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="0"/>
-        <v>497</v>
+      <c r="B10" s="4">
+        <f>SUM(B4:B9)</f>
+        <v>112</v>
+      </c>
+      <c r="C10" s="4">
+        <f>SUM(C4:C9)</f>
+        <v>107</v>
+      </c>
+      <c r="D10" s="4">
+        <f>SUM(D4:D9)</f>
+        <v>92</v>
+      </c>
+      <c r="E10" s="4">
+        <f>SUM(E4:E9)</f>
+        <v>89</v>
+      </c>
+      <c r="F10" s="4">
+        <f>SUM(F4:F9)</f>
+        <v>117</v>
+      </c>
+      <c r="G10" s="4">
+        <f>SUM(B10:F10)</f>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2651,72 +2801,80 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="2" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>102</v>
+        <v>69</v>
+      </c>
+      <c r="B4" s="8">
+        <v>2.0299999999999998</v>
       </c>
       <c r="C4" s="8">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="D4" s="8">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="E4" s="8">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="18">
-        <f>AVERAGE(B4:E4)</f>
-        <v>2.1366666666666667</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+        <v>70</v>
+      </c>
+      <c r="B5" s="17">
+        <f>AVERAGE(B4:F4)</f>
+        <v>2.1520000000000001</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2725,94 +2883,98 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="8">
-        <f>25+1</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="8">
         <v>21</v>
       </c>
       <c r="D4" s="8">
-        <f>22+1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="8">
-        <f>7+1</f>
-        <v>8</v>
-      </c>
-      <c r="F4" s="7">
-        <f>SUM(B4:E4)</f>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="F4" s="8">
+        <v>19</v>
+      </c>
+      <c r="G4" s="7">
+        <f>SUM(B4:F4)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="8">
-        <f>13.75+12</f>
-        <v>25.75</v>
+        <v>13.75</v>
       </c>
       <c r="C5" s="8">
         <v>23.25</v>
       </c>
       <c r="D5" s="8">
-        <f>19+15.5</f>
-        <v>34.5</v>
+        <v>19</v>
       </c>
       <c r="E5" s="8">
-        <f>5+26</f>
-        <v>31</v>
-      </c>
-      <c r="F5" s="7">
-        <f>SUM(B5:E5)</f>
-        <v>114.5</v>
+        <v>5</v>
+      </c>
+      <c r="F5" s="8">
+        <v>12.25</v>
+      </c>
+      <c r="G5" s="7">
+        <f>SUM(B5:F5)</f>
+        <v>73.25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2820,41 +2982,45 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3724B3-610D-B645-9E33-D85F4FB536C4}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B72C5E1-D8EF-BD4B-9990-2660E94F2C3D}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="E3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>
@@ -2868,14 +3034,17 @@
       <c r="E4" s="8">
         <v>8</v>
       </c>
-      <c r="F4" s="7">
-        <f>SUM(B4:E4)</f>
-        <v>10</v>
+      <c r="F4" s="8">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7">
+        <f>SUM(B4:F4)</f>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Desktop/T/BDESIGN/DASHBOARD/__INTERACTIVO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://savillsglobal-my.sharepoint.com/personal/oscar_nieto_savills_es/Documents/Archivos de chat de Microsoft Teams/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D243B-7CED-E64E-BDFF-E29013313185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{A89D243B-7CED-E64E-BDFF-E29013313185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94ADA68F-4576-43E6-92A7-705F8C539229}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3264" yWindow="2664" windowWidth="17436" windowHeight="9756" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="111">
   <si>
     <t>PLANTILLA DASHBOARD BDESIGN</t>
   </si>
@@ -252,9 +252,6 @@
     <t>Métrica</t>
   </si>
   <si>
-    <t>Días medios de entrega</t>
-  </si>
-  <si>
     <t>MEDIA YTD</t>
   </si>
   <si>
@@ -376,6 +373,9 @@
   </si>
   <si>
     <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Bdesign</t>
   </si>
 </sst>
 </file>
@@ -524,14 +524,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,6 +620,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -802,262 +806,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="9" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-    </row>
-    <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-    </row>
-    <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-    </row>
-    <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-    </row>
-    <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-    </row>
-    <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-    </row>
-    <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-    </row>
-    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="20" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-    </row>
-    <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-    </row>
-    <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-    </row>
-    <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-    </row>
-    <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-    </row>
-    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="29" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
@@ -1066,21 +1085,6 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1090,13 +1094,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>47</v>
       </c>
@@ -1107,78 +1111,86 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B4" s="8">
-        <v>23</v>
+        <f>23+7</f>
+        <v>30</v>
       </c>
       <c r="C4" s="8">
-        <v>28</v>
+        <f>28+10</f>
+        <v>38</v>
       </c>
       <c r="D4" s="8">
-        <v>23</v>
+        <f>23+8</f>
+        <v>31</v>
       </c>
       <c r="E4" s="8">
-        <v>25</v>
+        <f>25+9</f>
+        <v>34</v>
       </c>
       <c r="F4" s="8">
-        <v>38</v>
+        <f>38+8</f>
+        <v>46</v>
       </c>
       <c r="G4" s="9">
-        <f>SUM(B4:F4)</f>
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G4:G18" si="0">SUM(B4:F4)</f>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="8">
-        <v>25</v>
+        <f>25+1</f>
+        <v>26</v>
       </c>
       <c r="C5" s="8">
         <v>21</v>
       </c>
       <c r="D5" s="8">
-        <v>22</v>
+        <f>22+1</f>
+        <v>23</v>
       </c>
       <c r="E5" s="8">
-        <v>7</v>
+        <f>7+1</f>
+        <v>8</v>
       </c>
       <c r="F5" s="8">
         <v>20</v>
       </c>
       <c r="G5" s="9">
-        <f>SUM(B5:F5)</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1192,52 +1204,62 @@
         <v>12</v>
       </c>
       <c r="E6" s="8">
-        <v>13</v>
+        <f>13+2</f>
+        <v>15</v>
       </c>
       <c r="F6" s="8">
-        <v>18</v>
+        <f>18+1</f>
+        <v>19</v>
       </c>
       <c r="G6" s="9">
-        <f>SUM(B6:F6)</f>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="8">
+        <f>14+2</f>
+        <v>16</v>
+      </c>
+      <c r="C7" s="8">
+        <f>8+6</f>
         <v>14</v>
       </c>
-      <c r="C7" s="8">
-        <v>8</v>
-      </c>
       <c r="D7" s="8">
-        <v>11</v>
+        <f>11+3</f>
+        <v>14</v>
       </c>
       <c r="E7" s="8">
-        <v>11</v>
+        <f>11+10</f>
+        <v>21</v>
       </c>
       <c r="F7" s="8">
-        <v>12</v>
+        <f>12+4</f>
+        <v>16</v>
       </c>
       <c r="G7" s="9">
-        <f>SUM(B7:F7)</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="8">
+        <f>9+1</f>
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <f>6+1</f>
+        <v>7</v>
+      </c>
+      <c r="D8" s="8">
+        <f>7+2</f>
         <v>9</v>
-      </c>
-      <c r="C8" s="8">
-        <v>6</v>
-      </c>
-      <c r="D8" s="8">
-        <v>7</v>
       </c>
       <c r="E8" s="8">
         <v>11</v>
@@ -1246,13 +1268,13 @@
         <v>3</v>
       </c>
       <c r="G8" s="9">
-        <f>SUM(B8:F8)</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="8">
         <v>5</v>
@@ -1270,13 +1292,13 @@
         <v>3</v>
       </c>
       <c r="G9" s="9">
-        <f>SUM(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="8">
         <v>3</v>
@@ -1294,37 +1316,42 @@
         <v>8</v>
       </c>
       <c r="G10" s="9">
-        <f>SUM(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="8">
-        <v>9</v>
+        <f>9+1</f>
+        <v>10</v>
       </c>
       <c r="C11" s="8">
+        <f>4+6</f>
+        <v>10</v>
+      </c>
+      <c r="D11" s="8">
+        <f>4+3</f>
+        <v>7</v>
+      </c>
+      <c r="E11" s="8">
+        <f>3+2</f>
+        <v>5</v>
+      </c>
+      <c r="F11" s="8">
+        <f>3+1</f>
         <v>4</v>
       </c>
-      <c r="D11" s="8">
-        <v>4</v>
-      </c>
-      <c r="E11" s="8">
-        <v>3</v>
-      </c>
-      <c r="F11" s="8">
-        <v>3</v>
-      </c>
       <c r="G11" s="9">
-        <f>SUM(B11:F11)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
@@ -1332,24 +1359,30 @@
       <c r="C12" s="8">
         <v>1</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
       <c r="F12" s="8">
         <v>7</v>
       </c>
       <c r="G12" s="9">
-        <f>SUM(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="8">
         <v>4</v>
       </c>
-      <c r="C13" s="8"/>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
       <c r="D13" s="8">
         <v>1</v>
       </c>
@@ -1360,16 +1393,17 @@
         <v>2</v>
       </c>
       <c r="G13" s="9">
-        <f>SUM(B13:F13)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="C14" s="8">
         <v>2</v>
@@ -1382,93 +1416,113 @@
         <v>2</v>
       </c>
       <c r="G14" s="9">
-        <f>SUM(B14:F14)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="8">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="8">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+      <c r="D15" s="8">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="B15" s="8">
-        <v>2</v>
-      </c>
-      <c r="C15" s="8">
-        <v>2</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9">
-        <f>SUM(B15:F15)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="B16" s="8">
         <v>3</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="8">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2</v>
+      </c>
       <c r="E16" s="8">
         <v>1</v>
       </c>
       <c r="F16" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="G16" s="9">
-        <f>SUM(B16:F16)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
       <c r="E17" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
       <c r="G17" s="10">
-        <f>SUM(B17:F17)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B18" s="11">
         <f>SUM(B4:B17)</f>
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C18" s="11">
         <f>SUM(C4:C17)</f>
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D18" s="11">
         <f>SUM(D4:D17)</f>
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E18" s="11">
         <f>SUM(E4:E17)</f>
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F18" s="11">
         <f>SUM(F4:F17)</f>
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="G18" s="11">
-        <f>SUM(B18:F18)</f>
-        <v>517</v>
+        <f t="shared" si="0"/>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -1483,13 +1537,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>55</v>
       </c>
@@ -1500,35 +1554,36 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8">
-        <v>26</v>
+        <f>26+1</f>
+        <v>27</v>
       </c>
       <c r="C4" s="8">
         <v>24</v>
@@ -1537,17 +1592,19 @@
         <v>20</v>
       </c>
       <c r="E4" s="8">
+        <f>18+2</f>
+        <v>20</v>
+      </c>
+      <c r="F4" s="8">
+        <f>15+3</f>
         <v>18</v>
       </c>
-      <c r="F4" s="8">
-        <v>15</v>
-      </c>
       <c r="G4" s="8">
-        <f>SUM(B4:F4)</f>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G4:G25" si="0">SUM(B4:F4)</f>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
@@ -1567,13 +1624,13 @@
         <v>36</v>
       </c>
       <c r="G5" s="8">
-        <f>SUM(B5:F5)</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="8">
         <v>14</v>
@@ -1591,13 +1648,13 @@
         <v>9</v>
       </c>
       <c r="G6" s="8">
-        <f>SUM(B6:F6)</f>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="8">
         <v>7</v>
@@ -1609,17 +1666,18 @@
         <v>16</v>
       </c>
       <c r="E7" s="8">
-        <v>13</v>
+        <f>13+1</f>
+        <v>14</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
       </c>
       <c r="G7" s="8">
-        <f>SUM(B7:F7)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -1627,7 +1685,8 @@
         <v>10</v>
       </c>
       <c r="C8" s="8">
-        <v>10</v>
+        <f>10+1</f>
+        <v>11</v>
       </c>
       <c r="D8" s="8">
         <v>5</v>
@@ -1639,13 +1698,13 @@
         <v>6</v>
       </c>
       <c r="G8" s="8">
-        <f>SUM(B8:F8)</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B9" s="8">
         <v>5</v>
@@ -1663,13 +1722,13 @@
         <v>17</v>
       </c>
       <c r="G9" s="8">
-        <f>SUM(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="8">
         <v>12</v>
@@ -1687,22 +1746,24 @@
         <v>3</v>
       </c>
       <c r="G10" s="8">
-        <f>SUM(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="8">
-        <v>5</v>
+        <f>5+1</f>
+        <v>6</v>
       </c>
       <c r="C11" s="8">
         <v>4</v>
       </c>
       <c r="D11" s="8">
-        <v>5</v>
+        <f>5+2</f>
+        <v>7</v>
       </c>
       <c r="E11" s="8">
         <v>3</v>
@@ -1711,11 +1772,11 @@
         <v>7</v>
       </c>
       <c r="G11" s="8">
-        <f>SUM(B11:F11)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
@@ -1735,57 +1796,65 @@
         <v>7</v>
       </c>
       <c r="G12" s="8">
-        <f>SUM(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>3</v>
+        <f>3+12</f>
+        <v>15</v>
       </c>
       <c r="C13" s="8">
-        <v>2</v>
+        <f>2+23</f>
+        <v>25</v>
       </c>
       <c r="D13" s="8">
-        <v>3</v>
-      </c>
-      <c r="E13" s="8"/>
+        <f>3+18</f>
+        <v>21</v>
+      </c>
+      <c r="E13" s="8">
+        <v>23</v>
+      </c>
       <c r="F13" s="8">
-        <v>2</v>
+        <f>2+13</f>
+        <v>15</v>
       </c>
       <c r="G13" s="8">
-        <f>SUM(B13:F13)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8">
         <v>3</v>
       </c>
       <c r="D14" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="E14" s="8">
         <v>1</v>
       </c>
       <c r="F14" s="8">
-        <v>3</v>
+        <f>3+1</f>
+        <v>4</v>
       </c>
       <c r="G14" s="8">
-        <f>SUM(B14:F14)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8">
@@ -1799,35 +1868,39 @@
         <v>3</v>
       </c>
       <c r="G15" s="8">
-        <f>SUM(B15:F15)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" s="8">
-        <v>1</v>
+        <f>1+2</f>
+        <v>3</v>
       </c>
       <c r="C16" s="8">
         <v>2</v>
       </c>
-      <c r="D16" s="8"/>
+      <c r="D16" s="8">
+        <v>2</v>
+      </c>
       <c r="E16" s="8">
         <v>3</v>
       </c>
       <c r="F16" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="G16" s="8">
-        <f>SUM(B16:F16)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" s="8">
         <v>3</v>
@@ -1841,19 +1914,20 @@
         <v>2</v>
       </c>
       <c r="G17" s="8">
-        <f>SUM(B17:F17)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" s="8">
         <v>2</v>
       </c>
       <c r="C18" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="D18" s="8">
         <v>1</v>
@@ -1863,13 +1937,13 @@
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8">
-        <f>SUM(B18:F18)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
@@ -1883,13 +1957,13 @@
         <v>2</v>
       </c>
       <c r="G19" s="8">
-        <f>SUM(B19:F19)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20" s="8">
         <v>1</v>
@@ -1905,13 +1979,13 @@
         <v>1</v>
       </c>
       <c r="G20" s="8">
-        <f>SUM(B20:F20)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8">
@@ -1923,13 +1997,13 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8">
-        <f>SUM(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1939,31 +2013,34 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8">
-        <f>SUM(B22:F22)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8">
         <v>1</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
       <c r="F23" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="G23" s="8">
-        <f>SUM(B23:F23)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="8">
         <v>1</v>
@@ -1973,37 +2050,37 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8">
-        <f>SUM(B24:F24)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B25" s="4">
         <f>SUM(B4:B24)</f>
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C25" s="4">
         <f>SUM(C4:C24)</f>
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D25" s="4">
         <f>SUM(D4:D24)</f>
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E25" s="4">
         <f>SUM(E4:E24)</f>
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="F25" s="4">
         <f>SUM(F4:F24)</f>
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="G25" s="4">
-        <f>SUM(B25:F25)</f>
-        <v>517</v>
+        <f t="shared" si="0"/>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -2018,13 +2095,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>61</v>
       </c>
@@ -2035,35 +2112,36 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="8">
-        <v>165.5</v>
+        <f>165.5+0.5</f>
+        <v>166</v>
       </c>
       <c r="C4" s="8">
         <v>279.75</v>
@@ -2078,11 +2156,11 @@
         <v>191</v>
       </c>
       <c r="G4" s="7">
-        <f>SUM(B4:F4)</f>
-        <v>923.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G4:G27" si="0">SUM(B4:F4)</f>
+        <v>923.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
@@ -2102,13 +2180,13 @@
         <v>110.25</v>
       </c>
       <c r="G5" s="7">
-        <f>SUM(B5:F5)</f>
+        <f t="shared" si="0"/>
         <v>399.55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="8">
         <v>26.5</v>
@@ -2120,17 +2198,19 @@
         <v>102.5</v>
       </c>
       <c r="E6" s="8">
-        <v>58</v>
+        <f>58+9.5</f>
+        <v>67.5</v>
       </c>
       <c r="F6" s="8">
-        <v>25.75</v>
+        <f>25.75+7.5</f>
+        <v>33.25</v>
       </c>
       <c r="G6" s="7">
-        <f>SUM(B6:F6)</f>
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>58</v>
       </c>
@@ -2138,7 +2218,8 @@
         <v>89</v>
       </c>
       <c r="C7" s="8">
-        <v>65.5</v>
+        <f>65.5+3</f>
+        <v>68.5</v>
       </c>
       <c r="D7" s="8">
         <v>28</v>
@@ -2150,13 +2231,13 @@
         <v>19.75</v>
       </c>
       <c r="G7" s="7">
-        <f>SUM(B7:F7)</f>
-        <v>268.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>271.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="8">
         <v>29.25</v>
@@ -2168,19 +2249,20 @@
         <v>71.5</v>
       </c>
       <c r="E8" s="8">
-        <v>81</v>
+        <f>81+3</f>
+        <v>84</v>
       </c>
       <c r="F8" s="8">
         <v>1</v>
       </c>
       <c r="G8" s="7">
-        <f>SUM(B8:F8)</f>
-        <v>226.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>229.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="8">
         <v>74</v>
@@ -2198,13 +2280,13 @@
         <v>24.75</v>
       </c>
       <c r="G9" s="7">
-        <f>SUM(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>182.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="8">
         <v>13</v>
@@ -2222,22 +2304,24 @@
         <v>82</v>
       </c>
       <c r="G10" s="7">
-        <f>SUM(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>171.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="8">
-        <v>16.75</v>
+        <f>16.75+20.5</f>
+        <v>37.25</v>
       </c>
       <c r="C11" s="8">
         <v>8</v>
       </c>
       <c r="D11" s="8">
-        <v>38</v>
+        <f>38+31.5</f>
+        <v>69.5</v>
       </c>
       <c r="E11" s="8">
         <v>40.5</v>
@@ -2246,11 +2330,11 @@
         <v>37.5</v>
       </c>
       <c r="G11" s="7">
-        <f>SUM(B11:F11)</f>
-        <v>140.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>192.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
@@ -2270,13 +2354,13 @@
         <v>32.5</v>
       </c>
       <c r="G12" s="7">
-        <f>SUM(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>106.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="8">
         <v>9</v>
@@ -2294,13 +2378,13 @@
         <v>5</v>
       </c>
       <c r="G13" s="7">
-        <f>SUM(B13:F13)</f>
+        <f t="shared" si="0"/>
         <v>62.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8">
@@ -2314,13 +2398,13 @@
         <v>48</v>
       </c>
       <c r="G14" s="7">
-        <f>SUM(B14:F14)</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="8">
         <v>39.5</v>
@@ -2334,13 +2418,13 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="7">
-        <f>SUM(B15:F15)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="8">
         <v>4.5</v>
@@ -2356,79 +2440,91 @@
         <v>4</v>
       </c>
       <c r="G16" s="7">
-        <f>SUM(B16:F16)</f>
+        <f t="shared" si="0"/>
         <v>27.75</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="8">
-        <v>13.5</v>
+        <f>13.5+72.55</f>
+        <v>86.05</v>
       </c>
       <c r="C17" s="8">
-        <v>3.75</v>
+        <f>3.75+240.5</f>
+        <v>244.25</v>
       </c>
       <c r="D17" s="8">
-        <v>5.75</v>
-      </c>
-      <c r="E17" s="8"/>
+        <f>5.75+207.5</f>
+        <v>213.25</v>
+      </c>
+      <c r="E17" s="8">
+        <v>125.25</v>
+      </c>
       <c r="F17" s="8">
-        <v>4</v>
+        <f>4+75</f>
+        <v>79</v>
       </c>
       <c r="G17" s="7">
-        <f>SUM(B17:F17)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>747.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8">
         <v>14.5</v>
       </c>
       <c r="D18" s="8">
-        <v>5</v>
+        <f>5+1</f>
+        <v>6</v>
       </c>
       <c r="E18" s="8">
         <v>4</v>
       </c>
       <c r="F18" s="8">
-        <v>3.25</v>
+        <f>3.25+27.5</f>
+        <v>30.75</v>
       </c>
       <c r="G18" s="7">
-        <f>SUM(B18:F18)</f>
-        <v>26.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>55.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" s="8">
-        <v>3</v>
+        <f>3+22</f>
+        <v>25</v>
       </c>
       <c r="C19" s="8">
         <v>4</v>
       </c>
-      <c r="D19" s="8"/>
+      <c r="D19" s="8">
+        <v>4.25</v>
+      </c>
       <c r="E19" s="8">
         <v>16.75</v>
       </c>
       <c r="F19" s="8">
-        <v>1</v>
+        <f>1+1.25</f>
+        <v>2.25</v>
       </c>
       <c r="G19" s="7">
-        <f>SUM(B19:F19)</f>
-        <v>24.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2438,31 +2534,34 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="7">
-        <f>SUM(B20:F20)</f>
+        <f t="shared" si="0"/>
         <v>24.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8">
         <v>13</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="8">
+        <v>6</v>
+      </c>
       <c r="F21" s="8">
-        <v>3</v>
+        <f>3+11.5</f>
+        <v>14.5</v>
       </c>
       <c r="G21" s="7">
-        <f>SUM(B21:F21)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" s="8">
         <v>12</v>
@@ -2472,13 +2571,13 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="7">
-        <f>SUM(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
@@ -2490,13 +2589,13 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="7">
-        <f>SUM(B23:F23)</f>
+        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8">
@@ -2510,19 +2609,20 @@
         <v>5</v>
       </c>
       <c r="G24" s="7">
-        <f>SUM(B24:F24)</f>
+        <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B25" s="8">
         <v>5</v>
       </c>
       <c r="C25" s="8">
-        <v>1</v>
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="D25" s="8">
         <v>1</v>
@@ -2532,13 +2632,13 @@
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="7">
-        <f>SUM(B25:F25)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -2548,37 +2648,37 @@
         <v>1</v>
       </c>
       <c r="G26" s="7">
-        <f>SUM(B26:F26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B27" s="4">
         <f>SUM(B4:B26)</f>
-        <v>674.5</v>
+        <v>790.05</v>
       </c>
       <c r="C27" s="4">
         <f>SUM(C4:C26)</f>
-        <v>627.25</v>
+        <v>871.75</v>
       </c>
       <c r="D27" s="4">
         <f>SUM(D4:D26)</f>
-        <v>580.25</v>
+        <v>824.5</v>
       </c>
       <c r="E27" s="4">
         <f>SUM(E4:E26)</f>
-        <v>568.04999999999995</v>
+        <v>711.8</v>
       </c>
       <c r="F27" s="4">
         <f>SUM(F4:F26)</f>
-        <v>603.25</v>
+        <v>726</v>
       </c>
       <c r="G27" s="4">
-        <f>SUM(B27:F27)</f>
-        <v>3053.3</v>
+        <f t="shared" si="0"/>
+        <v>3924.1000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -2593,13 +2693,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>62</v>
       </c>
@@ -2610,86 +2710,98 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="8">
-        <v>78</v>
+        <f>78+10</f>
+        <v>88</v>
       </c>
       <c r="C4" s="8">
-        <v>73</v>
+        <f>73+20</f>
+        <v>93</v>
       </c>
       <c r="D4" s="8">
-        <v>67</v>
+        <f>67+22</f>
+        <v>89</v>
       </c>
       <c r="E4" s="8">
-        <v>58</v>
+        <f>58+25</f>
+        <v>83</v>
       </c>
       <c r="F4" s="8">
-        <v>90</v>
+        <f>90+16</f>
+        <v>106</v>
       </c>
       <c r="G4" s="7">
-        <f>SUM(B4:F4)</f>
-        <v>366</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G4:G10" si="0">SUM(B4:F4)</f>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B5" s="8">
-        <v>27</v>
+        <f>27+3</f>
+        <v>30</v>
       </c>
       <c r="C5" s="8">
-        <v>14</v>
+        <f>14+3</f>
+        <v>17</v>
       </c>
       <c r="D5" s="8">
-        <v>18</v>
+        <f>18+2</f>
+        <v>20</v>
       </c>
       <c r="E5" s="8">
-        <v>15</v>
+        <f>1+15</f>
+        <v>16</v>
       </c>
       <c r="F5" s="8">
-        <v>10</v>
+        <f>10+1</f>
+        <v>11</v>
       </c>
       <c r="G5" s="7">
-        <f>SUM(B5:F5)</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B6" s="8">
-        <v>4</v>
+        <f>4+3</f>
+        <v>7</v>
       </c>
       <c r="C6" s="8">
-        <v>13</v>
+        <f>13+1</f>
+        <v>14</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
@@ -2701,33 +2813,36 @@
         <v>13</v>
       </c>
       <c r="G6" s="7">
-        <f>SUM(B6:F6)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8">
-        <v>5</v>
+        <f>5+1</f>
+        <v>6</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
       <c r="F7" s="8">
         <v>1</v>
       </c>
       <c r="G7" s="7">
-        <f>SUM(B7:F7)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" s="8">
         <v>3</v>
@@ -2741,13 +2856,13 @@
         <v>2</v>
       </c>
       <c r="G8" s="7">
-        <f>SUM(B8:F8)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2757,37 +2872,37 @@
         <v>1</v>
       </c>
       <c r="G9" s="7">
-        <f>SUM(B9:F9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="4">
         <f>SUM(B4:B9)</f>
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C10" s="4">
         <f>SUM(C4:C9)</f>
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D10" s="4">
         <f>SUM(D4:D9)</f>
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E10" s="4">
         <f>SUM(E4:E9)</f>
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="F10" s="4">
         <f>SUM(F4:F9)</f>
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="G10" s="4">
-        <f>SUM(B10:F10)</f>
-        <v>517</v>
+        <f t="shared" si="0"/>
+        <v>626</v>
       </c>
     </row>
   </sheetData>
@@ -2801,14 +2916,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>67</v>
       </c>
@@ -2818,29 +2933,29 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="B4" s="8">
         <v>2.0299999999999998</v>
@@ -2858,23 +2973,43 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="17">
-        <f>AVERAGE(B4:F4)</f>
-        <v>2.1520000000000001</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="8">
+        <v>2.06</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1.84</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1.63</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="17">
+        <f>AVERAGE(B4:F5)</f>
+        <v>1.9590000000000001</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2884,15 +3019,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -2901,75 +3036,81 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="8">
-        <v>25</v>
+        <f>25+1</f>
+        <v>26</v>
       </c>
       <c r="C4" s="8">
         <v>21</v>
       </c>
       <c r="D4" s="8">
-        <v>22</v>
+        <f>22+1</f>
+        <v>23</v>
       </c>
       <c r="E4" s="8">
-        <v>7</v>
+        <f>7+1</f>
+        <v>8</v>
       </c>
       <c r="F4" s="8">
         <v>19</v>
       </c>
       <c r="G4" s="7">
         <f>SUM(B4:F4)</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="8">
-        <v>13.75</v>
+        <f>13.75+11.5</f>
+        <v>25.25</v>
       </c>
       <c r="C5" s="8">
         <v>23.25</v>
       </c>
       <c r="D5" s="8">
-        <v>19</v>
+        <f>19+15.5</f>
+        <v>34.5</v>
       </c>
       <c r="E5" s="8">
-        <v>5</v>
+        <f>5+26</f>
+        <v>31</v>
       </c>
       <c r="F5" s="8">
         <v>12.25</v>
       </c>
       <c r="G5" s="7">
         <f>SUM(B5:F5)</f>
-        <v>73.25</v>
+        <v>126.25</v>
       </c>
     </row>
   </sheetData>
@@ -2984,11 +3125,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B72C5E1-D8EF-BD4B-9990-2660E94F2C3D}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -2997,30 +3138,30 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="8">
         <v>2</v>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://savillsglobal-my.sharepoint.com/personal/oscar_nieto_savills_es/Documents/Archivos de chat de Microsoft Teams/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{A89D243B-7CED-E64E-BDFF-E29013313185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94ADA68F-4576-43E6-92A7-705F8C539229}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{AA2F3D6D-A419-274F-94AA-1738E20DBB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0678C3E-F8DD-4BE9-83CD-95931D124269}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3264" yWindow="2664" windowWidth="17436" windowHeight="9756" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="114">
   <si>
     <t>PLANTILLA DASHBOARD BDESIGN</t>
   </si>
@@ -376,6 +376,15 @@
   </si>
   <si>
     <t>Bdesign</t>
+  </si>
+  <si>
+    <t>Formacion</t>
+  </si>
+  <si>
+    <t>Junio</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -492,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -514,12 +523,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -620,10 +623,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -813,12 +812,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -829,31 +828,31 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -864,71 +863,71 @@
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
     </row>
     <row r="20" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -939,51 +938,51 @@
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
     </row>
     <row r="29" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -994,71 +993,71 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -1093,25 +1092,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="7" width="14" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
@@ -1131,10 +1131,13 @@
         <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>50</v>
       </c>
@@ -1155,15 +1158,19 @@
         <v>34</v>
       </c>
       <c r="F4" s="8">
-        <f>38+8</f>
+        <f>36+9</f>
+        <v>45</v>
+      </c>
+      <c r="G4" s="8">
+        <f>36+10</f>
         <v>46</v>
       </c>
-      <c r="G4" s="9">
-        <f t="shared" ref="G4:G18" si="0">SUM(B4:F4)</f>
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="8">
+        <f>SUM(B4:G4)</f>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>45</v>
       </c>
@@ -1179,18 +1186,21 @@
         <v>23</v>
       </c>
       <c r="E5" s="8">
-        <f>7+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="8">
-        <v>20</v>
-      </c>
-      <c r="G5" s="9">
-        <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="G5" s="8">
+        <f>29+1</f>
+        <v>30</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" ref="H5:H18" si="0">SUM(B5:G5)</f>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1211,18 +1221,22 @@
         <f>18+1</f>
         <v>19</v>
       </c>
-      <c r="G6" s="9">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="8">
+        <f>36+2</f>
+        <v>38</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>73</v>
       </c>
       <c r="B7" s="8">
-        <f>14+2</f>
-        <v>16</v>
+        <f>14+3</f>
+        <v>17</v>
       </c>
       <c r="C7" s="8">
         <f>8+6</f>
@@ -1240,12 +1254,16 @@
         <f>12+4</f>
         <v>16</v>
       </c>
-      <c r="G7" s="9">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="8">
+        <f>5+3</f>
+        <v>8</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
@@ -1258,69 +1276,85 @@
         <v>7</v>
       </c>
       <c r="D8" s="8">
-        <f>7+2</f>
-        <v>9</v>
+        <f>6+2</f>
+        <v>8</v>
       </c>
       <c r="E8" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="8">
         <v>3</v>
       </c>
-      <c r="G8" s="9">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="8">
+        <f>11+1</f>
+        <v>12</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="8">
         <v>5</v>
       </c>
-      <c r="C9" s="8">
-        <v>8</v>
-      </c>
       <c r="D9" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="8">
         <v>6</v>
       </c>
       <c r="F9" s="8">
-        <v>3</v>
-      </c>
-      <c r="G9" s="9">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="G9" s="8">
+        <v>11</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B10" s="8">
-        <v>3</v>
+        <f>5+1</f>
+        <v>6</v>
       </c>
       <c r="C10" s="8">
-        <v>5</v>
+        <f>8+1</f>
+        <v>9</v>
       </c>
       <c r="D10" s="8">
-        <v>4</v>
+        <f>6+1</f>
+        <v>7</v>
       </c>
       <c r="E10" s="8">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="8">
+        <f>3+3</f>
         <v>6</v>
       </c>
-      <c r="F10" s="8">
-        <v>8</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="8">
+        <f>5+1</f>
+        <v>6</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>75</v>
       </c>
@@ -1344,12 +1378,16 @@
         <f>3+1</f>
         <v>4</v>
       </c>
-      <c r="G11" s="9">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="8">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>80</v>
       </c>
@@ -1359,45 +1397,47 @@
       <c r="C12" s="8">
         <v>1</v>
       </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0</v>
-      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>7</v>
       </c>
-      <c r="G12" s="9">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="8">
+        <v>4</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="8">
         <v>4</v>
       </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
+      <c r="C13" s="8"/>
       <c r="D13" s="8">
-        <v>1</v>
+        <f>1+2</f>
+        <v>3</v>
       </c>
       <c r="E13" s="8">
         <v>2</v>
       </c>
       <c r="F13" s="8">
-        <v>2</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
+        <f>4+1</f>
+        <v>5</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>79</v>
       </c>
@@ -1415,119 +1455,148 @@
       <c r="F14" s="8">
         <v>2</v>
       </c>
-      <c r="G14" s="9">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14" s="8">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="8">
+        <v>3</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="G15" s="8">
+        <f>4+2</f>
+        <v>6</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B16" s="8">
+        <f>1+2</f>
+        <v>3</v>
+      </c>
+      <c r="C16" s="8">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="C15" s="8">
+      <c r="D16" s="8">
         <f>2+1</f>
         <v>3</v>
       </c>
-      <c r="D15" s="8">
-        <f>2+1</f>
-        <v>3</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="8">
-        <v>3</v>
-      </c>
-      <c r="C16" s="8">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2</v>
-      </c>
       <c r="E16" s="8">
         <v>1</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="8"/>
+      <c r="G16" s="8">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="G16" s="9">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="8">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="8">
-        <v>0</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="8">
         <v>1</v>
       </c>
       <c r="E17" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="10">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="11">
-        <f>SUM(B4:B17)</f>
-        <v>126</v>
-      </c>
-      <c r="C18" s="11">
-        <f>SUM(C4:C17)</f>
-        <v>131</v>
-      </c>
-      <c r="D18" s="11">
-        <f>SUM(D4:D17)</f>
-        <v>113</v>
-      </c>
-      <c r="E18" s="11">
-        <f>SUM(E4:E17)</f>
+      <c r="B19" s="9">
+        <f>SUM(B4:B18)</f>
+        <v>129</v>
+      </c>
+      <c r="C19" s="9">
+        <f>SUM(C4:C18)</f>
+        <v>132</v>
+      </c>
+      <c r="D19" s="9">
+        <f>SUM(D4:D18)</f>
+        <v>115</v>
+      </c>
+      <c r="E19" s="9">
+        <f>SUM(E4:E18)</f>
         <v>114</v>
       </c>
-      <c r="F18" s="11">
-        <f>SUM(F4:F17)</f>
-        <v>132</v>
-      </c>
-      <c r="G18" s="11">
-        <f t="shared" si="0"/>
-        <v>616</v>
+      <c r="F19" s="9">
+        <f t="shared" ref="B19:H19" si="1">SUM(F4:F18)</f>
+        <v>134</v>
+      </c>
+      <c r="G19" s="9">
+        <f t="shared" si="1"/>
+        <v>177</v>
+      </c>
+      <c r="H19" s="9">
+        <f t="shared" si="1"/>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1536,25 +1605,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="7" width="14" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -1574,10 +1644,13 @@
         <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>82</v>
       </c>
@@ -1600,16 +1673,19 @@
         <v>18</v>
       </c>
       <c r="G4" s="8">
-        <f t="shared" ref="G4:G25" si="0">SUM(B4:F4)</f>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="H4" s="8">
+        <f>SUM(B4:G4)</f>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="8">
         <v>20</v>
@@ -1621,14 +1697,17 @@
         <v>19</v>
       </c>
       <c r="F5" s="8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" ref="H5:H25" si="0">SUM(B5:G5)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>83</v>
       </c>
@@ -1648,36 +1727,41 @@
         <v>9</v>
       </c>
       <c r="G6" s="8">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B7" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D7" s="8">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E7" s="8">
-        <f>13+1</f>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F7" s="8">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -1698,35 +1782,42 @@
         <v>6</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9" s="8">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E9" s="8">
-        <v>5</v>
+        <f>13+1</f>
+        <v>14</v>
       </c>
       <c r="F9" s="8">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G9" s="8">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>85</v>
       </c>
@@ -1746,11 +1837,14 @@
         <v>3</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>86</v>
       </c>
@@ -1762,186 +1856,208 @@
         <v>4</v>
       </c>
       <c r="D11" s="8">
+        <f>5+3</f>
+        <v>8</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3</v>
+      </c>
+      <c r="F11" s="8">
+        <v>7</v>
+      </c>
+      <c r="G11" s="8">
+        <f>6+8</f>
+        <v>14</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="8">
+        <v>3</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8">
+        <v>3</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3</v>
+      </c>
+      <c r="F12" s="8">
+        <v>7</v>
+      </c>
+      <c r="G12" s="8">
+        <v>4</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <f>3+1</f>
+        <v>4</v>
+      </c>
+      <c r="G13" s="8">
+        <v>7</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="8">
+        <f>1+2</f>
+        <v>3</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="8">
         <f>5+2</f>
         <v>7</v>
       </c>
-      <c r="E11" s="8">
-        <v>3</v>
-      </c>
-      <c r="F11" s="8">
-        <v>7</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="8">
-        <v>3</v>
-      </c>
-      <c r="C12" s="8">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8">
-        <v>4</v>
-      </c>
-      <c r="E12" s="8">
-        <v>4</v>
-      </c>
-      <c r="F12" s="8">
-        <v>7</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="H14" s="8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="8">
+        <v>2</v>
+      </c>
+      <c r="C15" s="8">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8">
+        <v>5</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="8">
-        <f>3+12</f>
-        <v>15</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B16" s="8">
+        <f>3+13</f>
+        <v>16</v>
+      </c>
+      <c r="C16" s="8">
         <f>2+23</f>
         <v>25</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D16" s="8">
         <f>3+18</f>
         <v>21</v>
       </c>
-      <c r="E13" s="8">
-        <v>23</v>
-      </c>
-      <c r="F13" s="8">
-        <f>2+13</f>
-        <v>15</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="0"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8">
+      <c r="E16" s="8">
+        <v>22</v>
+      </c>
+      <c r="F16" s="8">
+        <v>14</v>
+      </c>
+      <c r="G16" s="8">
+        <v>18</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8">
+        <v>2</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8">
+        <v>2</v>
+      </c>
+      <c r="F17" s="8">
         <v>3</v>
       </c>
-      <c r="D14" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8">
-        <f>3+1</f>
-        <v>4</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8">
-        <v>2</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8">
-        <v>2</v>
-      </c>
-      <c r="F15" s="8">
+      <c r="G17" s="8">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="8">
+      <c r="C18" s="8">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8">
+        <v>2</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="8">
-        <f>1+2</f>
-        <v>3</v>
-      </c>
-      <c r="C16" s="8">
-        <v>2</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3</v>
-      </c>
-      <c r="F16" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="8">
-        <v>3</v>
-      </c>
-      <c r="C17" s="8">
-        <v>2</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8">
-        <v>2</v>
-      </c>
-      <c r="G17" s="8">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="8">
-        <v>2</v>
-      </c>
-      <c r="C18" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>93</v>
       </c>
@@ -1956,12 +2072,13 @@
       <c r="F19" s="8">
         <v>2</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="8"/>
+      <c r="H19" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>95</v>
       </c>
@@ -1979,29 +2096,37 @@
         <v>1</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="8">
-        <v>2</v>
-      </c>
+      <c r="C21" s="8"/>
       <c r="D21" s="8">
         <v>1</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1</v>
+      </c>
       <c r="G21" s="8">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>96</v>
       </c>
@@ -2013,79 +2138,104 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="C23" s="8">
+        <v>2</v>
+      </c>
       <c r="D23" s="8">
         <v>1</v>
       </c>
-      <c r="E23" s="8">
-        <v>1</v>
-      </c>
-      <c r="F23" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="8">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="F24" s="8">
+        <v>1</v>
+      </c>
       <c r="G24" s="8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="8">
+        <v>1</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="4">
-        <f>SUM(B4:B24)</f>
+      <c r="B26" s="4">
+        <f t="shared" ref="B26:H26" si="1">SUM(B4:B25)</f>
         <v>129</v>
       </c>
-      <c r="C25" s="4">
-        <f>SUM(C4:C24)</f>
+      <c r="C26" s="4">
+        <f t="shared" si="1"/>
         <v>132</v>
       </c>
-      <c r="D25" s="4">
-        <f>SUM(D4:D24)</f>
+      <c r="D26" s="4">
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
-      <c r="E25" s="4">
-        <f>SUM(E4:E24)</f>
-        <v>116</v>
-      </c>
-      <c r="F25" s="4">
-        <f>SUM(F4:F24)</f>
-        <v>135</v>
-      </c>
-      <c r="G25" s="4">
-        <f t="shared" si="0"/>
-        <v>627</v>
+      <c r="E26" s="4">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="1"/>
+        <v>179</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="1"/>
+        <v>799</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2094,25 +2244,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="7" width="14" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -2132,558 +2283,628 @@
         <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>99</v>
       </c>
       <c r="B4" s="8">
-        <f>165.5+0.5</f>
-        <v>166</v>
+        <f>224.75+0.5</f>
+        <v>225.25</v>
       </c>
       <c r="C4" s="8">
+        <v>189</v>
+      </c>
+      <c r="D4" s="8">
+        <v>160</v>
+      </c>
+      <c r="E4" s="8">
+        <v>127</v>
+      </c>
+      <c r="F4" s="8">
+        <f>165.5+1.5</f>
+        <v>167</v>
+      </c>
+      <c r="G4" s="8">
         <v>279.75</v>
       </c>
-      <c r="D4" s="8">
-        <v>127</v>
-      </c>
-      <c r="E4" s="8">
-        <v>160</v>
-      </c>
-      <c r="F4" s="8">
-        <v>191</v>
-      </c>
-      <c r="G4" s="7">
-        <f t="shared" ref="G4:G27" si="0">SUM(B4:F4)</f>
-        <v>923.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="8">
+        <f>SUM(B4:G4)</f>
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="8">
+        <v>103</v>
+      </c>
+      <c r="C5" s="8">
+        <v>96.25</v>
+      </c>
+      <c r="D5" s="8">
+        <v>60.8</v>
+      </c>
+      <c r="E5" s="8">
+        <v>53.25</v>
+      </c>
+      <c r="F5" s="8">
         <v>149.75</v>
       </c>
-      <c r="C5" s="8">
+      <c r="G5" s="8">
         <v>25.5</v>
       </c>
-      <c r="D5" s="8">
-        <v>53.25</v>
-      </c>
-      <c r="E5" s="8">
-        <v>60.8</v>
-      </c>
-      <c r="F5" s="8">
-        <v>110.25</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="0"/>
-        <v>399.55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="8">
+        <f t="shared" ref="H5:H26" si="0">SUM(B5:G5)</f>
+        <v>488.55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B6" s="8">
-        <v>26.5</v>
+        <v>70.55</v>
       </c>
       <c r="C6" s="8">
+        <v>26.75</v>
+      </c>
+      <c r="D6" s="8">
+        <v>60</v>
+      </c>
+      <c r="E6" s="8">
+        <f>102.5+9.5</f>
+        <v>112</v>
+      </c>
+      <c r="F6" s="8">
+        <f>27.5+6+27.5</f>
+        <v>61</v>
+      </c>
+      <c r="G6" s="8">
         <v>62.25</v>
       </c>
-      <c r="D6" s="8">
-        <v>102.5</v>
-      </c>
-      <c r="E6" s="8">
-        <f>58+9.5</f>
-        <v>67.5</v>
-      </c>
-      <c r="F6" s="8">
-        <f>25.75+7.5</f>
-        <v>33.25</v>
-      </c>
-      <c r="G6" s="7">
-        <f t="shared" si="0"/>
-        <v>292</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="8">
+        <f t="shared" si="0"/>
+        <v>392.55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="8">
+        <v>129.75</v>
+      </c>
+      <c r="C7" s="8">
+        <v>82</v>
+      </c>
+      <c r="D7" s="8">
+        <v>36</v>
+      </c>
+      <c r="E7" s="8">
+        <v>34.5</v>
+      </c>
+      <c r="F7" s="8">
+        <v>13</v>
+      </c>
+      <c r="G7" s="8">
+        <v>6</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="0"/>
+        <v>301.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B8" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="C8" s="8">
+        <f>19.75+3</f>
+        <v>22.75</v>
+      </c>
+      <c r="D8" s="8">
+        <v>66</v>
+      </c>
+      <c r="E8" s="8">
+        <v>28</v>
+      </c>
+      <c r="F8" s="8">
         <v>89</v>
       </c>
-      <c r="C7" s="8">
-        <f>65.5+3</f>
-        <v>68.5</v>
-      </c>
-      <c r="D7" s="8">
-        <v>28</v>
-      </c>
-      <c r="E7" s="8">
-        <v>66</v>
-      </c>
-      <c r="F7" s="8">
-        <v>19.75</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="0"/>
-        <v>271.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="G8" s="8">
+        <v>65.5</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="0"/>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>84</v>
+      </c>
+      <c r="E9" s="8">
+        <f>71.5+3</f>
+        <v>74.5</v>
+      </c>
+      <c r="F9" s="8">
         <v>29.25</v>
       </c>
-      <c r="C8" s="8">
+      <c r="G9" s="8">
         <v>43.5</v>
       </c>
-      <c r="D8" s="8">
-        <v>71.5</v>
-      </c>
-      <c r="E8" s="8">
-        <f>81+3</f>
-        <v>84</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
-        <f t="shared" si="0"/>
-        <v>229.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="H9" s="8">
+        <f t="shared" si="0"/>
+        <v>233.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
+      <c r="C10" s="8">
+        <v>24.75</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2</v>
+      </c>
+      <c r="E10" s="8">
+        <v>28.5</v>
+      </c>
+      <c r="F10" s="8">
         <v>74</v>
       </c>
-      <c r="C9" s="8">
+      <c r="G10" s="8">
         <v>53.5</v>
       </c>
-      <c r="D9" s="8">
-        <v>28.5</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2</v>
-      </c>
-      <c r="F9" s="8">
-        <v>24.75</v>
-      </c>
-      <c r="G9" s="7">
-        <f t="shared" si="0"/>
-        <v>182.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="8">
-        <v>13</v>
-      </c>
-      <c r="C10" s="8">
-        <v>6</v>
-      </c>
-      <c r="D10" s="8">
-        <v>34.5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>36</v>
-      </c>
-      <c r="F10" s="8">
-        <v>82</v>
-      </c>
-      <c r="G10" s="7">
-        <f t="shared" si="0"/>
-        <v>171.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="8">
+        <f t="shared" si="0"/>
+        <v>186.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>86</v>
       </c>
       <c r="B11" s="8">
-        <f>16.75+20.5</f>
-        <v>37.25</v>
+        <f>32+20.5</f>
+        <v>52.5</v>
       </c>
       <c r="C11" s="8">
-        <v>8</v>
+        <v>37.5</v>
       </c>
       <c r="D11" s="8">
-        <f>38+31.5</f>
-        <v>69.5</v>
+        <f>40.5+31.5</f>
+        <v>72</v>
       </c>
       <c r="E11" s="8">
-        <v>40.5</v>
+        <v>38</v>
       </c>
       <c r="F11" s="8">
-        <v>37.5</v>
-      </c>
-      <c r="G11" s="7">
-        <f t="shared" si="0"/>
-        <v>192.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16.75</v>
+      </c>
+      <c r="G11" s="8">
+        <f>8+19</f>
+        <v>27</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="0"/>
+        <v>243.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="8">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8">
+        <v>32.5</v>
+      </c>
+      <c r="D12" s="8">
+        <v>20.5</v>
+      </c>
+      <c r="E12" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="F12" s="8">
         <v>24.25</v>
       </c>
-      <c r="C12" s="8">
+      <c r="G12" s="8">
         <v>15</v>
       </c>
-      <c r="D12" s="8">
-        <v>13.5</v>
-      </c>
-      <c r="E12" s="8">
-        <v>21.5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>32.5</v>
-      </c>
-      <c r="G12" s="7">
-        <f t="shared" si="0"/>
-        <v>106.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="8">
+        <f t="shared" si="0"/>
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="8">
+        <v>7.75</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>17.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>18.25</v>
+      </c>
+      <c r="F13" s="8">
         <v>9</v>
       </c>
-      <c r="C13" s="8">
+      <c r="G13" s="8">
         <v>13</v>
       </c>
-      <c r="D13" s="8">
-        <v>18.25</v>
-      </c>
-      <c r="E13" s="8">
-        <v>17.5</v>
-      </c>
-      <c r="F13" s="8">
-        <v>5</v>
-      </c>
-      <c r="G13" s="7">
-        <f t="shared" si="0"/>
-        <v>62.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="8">
+        <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="8"/>
+      <c r="B14" s="8">
+        <v>10.5</v>
+      </c>
       <c r="C14" s="8">
+        <v>48</v>
+      </c>
+      <c r="D14" s="8">
+        <v>3</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8">
         <v>5</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8">
-        <v>3</v>
-      </c>
-      <c r="F14" s="8">
-        <v>48</v>
-      </c>
-      <c r="G14" s="7">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="8">
+        <f t="shared" si="0"/>
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="8">
-        <v>39.5</v>
-      </c>
+      <c r="B15" s="8"/>
       <c r="C15" s="8">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="G15" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="G15" s="8">
+        <v>8</v>
+      </c>
+      <c r="H15" s="8">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="8">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="D16" s="8">
+        <f>4+1</f>
+        <v>5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>5</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="0"/>
+        <v>47.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="8">
+        <f>17.75+22</f>
+        <v>39.75</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8">
+        <f>16.75+4.25</f>
+        <v>21</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8">
+        <f>3+1.25</f>
+        <v>4.25</v>
+      </c>
+      <c r="G17" s="8">
+        <f>4+28.6</f>
+        <v>32.6</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="0"/>
+        <v>98.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="8">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8">
+        <v>24.25</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8">
+        <f t="shared" si="0"/>
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="C16" s="8">
-        <v>10.5</v>
-      </c>
-      <c r="D16" s="8">
-        <v>8.75</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8">
-        <v>4</v>
-      </c>
-      <c r="G16" s="7">
-        <f t="shared" si="0"/>
-        <v>27.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="8">
-        <f>13.5+72.55</f>
-        <v>86.05</v>
-      </c>
-      <c r="C17" s="8">
-        <f>3.75+240.5</f>
-        <v>244.25</v>
-      </c>
-      <c r="D17" s="8">
-        <f>5.75+207.5</f>
-        <v>213.25</v>
-      </c>
-      <c r="E17" s="8">
-        <v>125.25</v>
-      </c>
-      <c r="F17" s="8">
-        <f>4+75</f>
-        <v>79</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="0"/>
-        <v>747.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8">
-        <v>14.5</v>
-      </c>
-      <c r="D18" s="8">
-        <f>5+1</f>
-        <v>6</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4</v>
-      </c>
-      <c r="F18" s="8">
-        <f>3.25+27.5</f>
-        <v>30.75</v>
-      </c>
-      <c r="G18" s="7">
-        <f t="shared" si="0"/>
-        <v>55.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="B19" s="8">
-        <f>3+22</f>
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C19" s="8">
         <v>4</v>
       </c>
-      <c r="D19" s="8">
-        <v>4.25</v>
-      </c>
+      <c r="D19" s="8"/>
       <c r="E19" s="8">
-        <v>16.75</v>
+        <v>8.75</v>
       </c>
       <c r="F19" s="8">
-        <f>1+1.25</f>
-        <v>2.25</v>
-      </c>
-      <c r="G19" s="7">
-        <f t="shared" si="0"/>
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4.5</v>
+      </c>
+      <c r="G19" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="0"/>
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="B20" s="8">
+        <v>77.55</v>
+      </c>
+      <c r="C20" s="8">
+        <f>6+240.5</f>
+        <v>246.5</v>
+      </c>
       <c r="D20" s="8">
-        <v>24.25</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="7">
-        <f t="shared" si="0"/>
-        <v>24.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>207.5</v>
+      </c>
+      <c r="E20" s="8">
+        <f>5.75+99.25</f>
+        <v>105</v>
+      </c>
+      <c r="F20" s="8">
+        <f>13.5+77</f>
+        <v>90.5</v>
+      </c>
+      <c r="G20" s="8">
+        <f>3.75+116</f>
+        <v>119.75</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="0"/>
+        <v>846.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="8"/>
+      <c r="B21" s="8">
+        <v>11</v>
+      </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="8">
-        <v>13</v>
-      </c>
+      <c r="D21" s="8"/>
       <c r="E21" s="8">
-        <v>6</v>
+        <f>13+6</f>
+        <v>19</v>
       </c>
       <c r="F21" s="8">
-        <f>3+11.5</f>
-        <v>14.5</v>
-      </c>
-      <c r="G21" s="7">
-        <f t="shared" si="0"/>
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11.5</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8">
+        <f t="shared" si="0"/>
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="8">
+        <v>7</v>
+      </c>
+      <c r="C22" s="8">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8">
+        <v>5</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8">
         <v>12</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="7">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8">
         <v>5</v>
       </c>
-      <c r="D23" s="8">
-        <v>6.5</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="7">
+      <c r="H24" s="8">
         <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8">
+      <c r="B25" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="C25" s="8">
+        <v>5</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8">
         <v>3.5</v>
       </c>
-      <c r="D24" s="8">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8">
-        <v>5</v>
-      </c>
-      <c r="G24" s="7">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="8">
-        <v>5</v>
-      </c>
-      <c r="C25" s="8">
-        <f>1+1</f>
-        <v>2</v>
-      </c>
-      <c r="D25" s="8">
-        <v>1</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="B26" s="8">
+        <v>1</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1</v>
+      </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="8">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B27" s="4">
-        <f>SUM(B4:B26)</f>
-        <v>790.05</v>
+        <f t="shared" ref="B27:H27" si="1">SUM(B4:B26)</f>
+        <v>792.84999999999991</v>
       </c>
       <c r="C27" s="4">
-        <f>SUM(C4:C26)</f>
-        <v>871.75</v>
+        <f t="shared" si="1"/>
+        <v>831.75</v>
       </c>
       <c r="D27" s="4">
-        <f>SUM(D4:D26)</f>
-        <v>824.5</v>
+        <f t="shared" si="1"/>
+        <v>816.3</v>
       </c>
       <c r="E27" s="4">
-        <f>SUM(E4:E26)</f>
-        <v>711.8</v>
+        <f t="shared" si="1"/>
+        <v>696</v>
       </c>
       <c r="F27" s="4">
-        <f>SUM(F4:F26)</f>
-        <v>726</v>
+        <f t="shared" si="1"/>
+        <v>800.25</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" si="0"/>
-        <v>3924.1000000000004</v>
+        <f t="shared" si="1"/>
+        <v>790.85</v>
+      </c>
+      <c r="H27" s="4">
+        <f t="shared" si="1"/>
+        <v>4728</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2692,25 +2913,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="7" width="14" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -2730,15 +2952,18 @@
         <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="8">
-        <f>78+10</f>
+        <f>77+9+2</f>
         <v>88</v>
       </c>
       <c r="C4" s="8">
@@ -2746,23 +2971,27 @@
         <v>93</v>
       </c>
       <c r="D4" s="8">
-        <f>67+22</f>
-        <v>89</v>
+        <f>66+21+1</f>
+        <v>88</v>
       </c>
       <c r="E4" s="8">
-        <f>58+25</f>
-        <v>83</v>
+        <f>57+24</f>
+        <v>81</v>
       </c>
       <c r="F4" s="8">
-        <f>90+16</f>
-        <v>106</v>
-      </c>
-      <c r="G4" s="7">
-        <f t="shared" ref="G4:G10" si="0">SUM(B4:F4)</f>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <f>87+17+1</f>
+        <v>105</v>
+      </c>
+      <c r="G4" s="8">
+        <f>98+18+1+1</f>
+        <v>118</v>
+      </c>
+      <c r="H4" s="8">
+        <f>SUM(B4:G4)</f>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -2779,19 +3008,23 @@
         <v>20</v>
       </c>
       <c r="E5" s="8">
-        <f>1+15</f>
+        <f>15+1</f>
         <v>16</v>
       </c>
       <c r="F5" s="8">
         <f>10+1</f>
         <v>11</v>
       </c>
-      <c r="G5" s="7">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="8">
+        <f>36+3</f>
+        <v>39</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" ref="H5:H9" si="0">SUM(B5:G5)</f>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>66</v>
       </c>
@@ -2812,12 +3045,15 @@
       <c r="F6" s="8">
         <v>13</v>
       </c>
-      <c r="G6" s="7">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="8">
+        <v>13</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>65</v>
       </c>
@@ -2827,20 +3063,26 @@
         <v>6</v>
       </c>
       <c r="D7" s="8">
+        <f>3</f>
         <v>3</v>
       </c>
       <c r="E7" s="8">
         <v>1</v>
       </c>
       <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="G7" s="8">
+        <f>1+3</f>
+        <v>4</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>100</v>
       </c>
@@ -2855,12 +3097,15 @@
       <c r="F8" s="8">
         <v>2</v>
       </c>
-      <c r="G8" s="7">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>109</v>
       </c>
@@ -2871,43 +3116,50 @@
       <c r="F9" s="8">
         <v>1</v>
       </c>
-      <c r="G9" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="4">
-        <f>SUM(B4:B9)</f>
+        <f t="shared" ref="B10:H10" si="1">SUM(B4:B9)</f>
         <v>128</v>
       </c>
       <c r="C10" s="4">
-        <f>SUM(C4:C9)</f>
+        <f t="shared" si="1"/>
         <v>132</v>
       </c>
       <c r="D10" s="4">
-        <f>SUM(D4:D9)</f>
-        <v>116</v>
+        <f t="shared" si="1"/>
+        <v>115</v>
       </c>
       <c r="E10" s="4">
-        <f>SUM(E4:E9)</f>
-        <v>116</v>
+        <f t="shared" si="1"/>
+        <v>114</v>
       </c>
       <c r="F10" s="4">
-        <f>SUM(F4:F9)</f>
+        <f t="shared" si="1"/>
         <v>134</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
-        <v>626</v>
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="1"/>
+        <v>799</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2916,24 +3168,25 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
@@ -2952,8 +3205,11 @@
       <c r="F3" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>110</v>
       </c>
@@ -2972,44 +3228,51 @@
       <c r="F4" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="8">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B5" s="8">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="C5" s="8">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="8">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="E5" s="8">
-        <v>1.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F5" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="17">
-        <f>AVERAGE(B4:F5)</f>
-        <v>1.9590000000000001</v>
-      </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="15">
+        <f>AVERAGE(B4:G5)</f>
+        <v>1.7891666666666672</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3018,25 +3281,26 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="7" width="14" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
@@ -3056,10 +3320,13 @@
         <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>71</v>
       </c>
@@ -3075,18 +3342,21 @@
         <v>23</v>
       </c>
       <c r="E4" s="8">
-        <f>7+1</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="8">
         <v>19</v>
       </c>
-      <c r="G4" s="7">
-        <f>SUM(B4:F4)</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="8">
+        <f>29+1</f>
+        <v>30</v>
+      </c>
+      <c r="H4" s="7">
+        <f>SUM(B4:G4)</f>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>72</v>
       </c>
@@ -3102,20 +3372,23 @@
         <v>34.5</v>
       </c>
       <c r="E5" s="8">
-        <f>5+26</f>
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F5" s="8">
         <v>12.25</v>
       </c>
-      <c r="G5" s="7">
-        <f>SUM(B5:F5)</f>
-        <v>126.25</v>
+      <c r="G5" s="8">
+        <f>14.55+0.5</f>
+        <v>15.05</v>
+      </c>
+      <c r="H5" s="7">
+        <f>SUM(B5:G5)</f>
+        <v>115.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3124,21 +3397,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B72C5E1-D8EF-BD4B-9990-2660E94F2C3D}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>102</v>
@@ -3156,10 +3430,13 @@
         <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>106</v>
       </c>
@@ -3178,14 +3455,17 @@
       <c r="F4" s="8">
         <v>3</v>
       </c>
-      <c r="G4" s="7">
-        <f>SUM(B4:F4)</f>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <f>SUM(B4:G4)</f>
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://savillsglobal-my.sharepoint.com/personal/oscar_nieto_savills_es/Documents/Archivos de chat de Microsoft Teams/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar.nieto/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{AA2F3D6D-A419-274F-94AA-1738E20DBB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0678C3E-F8DD-4BE9-83CD-95931D124269}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838C5438-8106-D640-8CBC-1D328AB19C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -527,14 +527,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -805,277 +805,262 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="9" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-    </row>
-    <row r="20" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-    </row>
-    <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-    </row>
-    <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-    </row>
-    <row r="29" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
@@ -1084,6 +1069,21 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1093,13 +1093,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>47</v>
       </c>
@@ -1111,7 +1111,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>50</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>45</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>73</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>52</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>76</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>74</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>75</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>80</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>53</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>79</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>78</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>77</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>81</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>111</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>114</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" ref="B19:H19" si="1">SUM(F4:F18)</f>
+        <f t="shared" ref="F19:H19" si="1">SUM(F4:F18)</f>
         <v>134</v>
       </c>
       <c r="G19" s="9">
@@ -1606,13 +1606,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>55</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>82</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>83</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>87</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>84</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>85</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>86</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>90</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>88</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>89</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>59</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>92</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>91</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>93</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>95</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>98</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>96</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>94</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>108</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>97</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>54</v>
       </c>
@@ -2245,13 +2245,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>61</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>99</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>57</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>488.55</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>82</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>392.55</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>87</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>84</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>233.25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>85</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>186.75</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>86</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>243.75</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>114.75</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>83</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>92</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>91</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>90</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>47.75</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>88</v>
       </c>
@@ -2659,15 +2659,15 @@
         <v>4.25</v>
       </c>
       <c r="G17" s="8">
-        <f>4+28.6</f>
-        <v>32.6</v>
+        <f>17.75+28.6</f>
+        <v>46.35</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
-        <v>98.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>112.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>96</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>32.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>95</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>29.75</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>59</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>846.8</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>98</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>89</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>97</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>94</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>93</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>108</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>54</v>
       </c>
@@ -2895,11 +2895,11 @@
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>790.85</v>
+        <v>804.6</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="1"/>
-        <v>4728</v>
+        <v>4741.75</v>
       </c>
     </row>
   </sheetData>
@@ -2914,13 +2914,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>63</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>66</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>65</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>100</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>109</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
@@ -3169,13 +3169,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>67</v>
       </c>
@@ -3186,7 +3186,7 @@
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>110</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>59</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>69</v>
       </c>
@@ -3282,13 +3282,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>70</v>
       </c>
@@ -3300,7 +3300,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>71</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>72</v>
       </c>
@@ -3398,9 +3398,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B72C5E1-D8EF-BD4B-9990-2660E94F2C3D}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>105</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>102</v>
@@ -3436,7 +3436,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>106</v>
       </c>
